--- a/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3932" uniqueCount="715">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3932" uniqueCount="718">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1745,6 +1745,9 @@
   <si>
     <t>obs-6
 vs-2</t>
+  </si>
+  <si>
+    <t>1792: target not supported</t>
   </si>
   <si>
     <t>value.nullFlavor</t>
@@ -2164,6 +2167,9 @@
 vs-3:If there is no a value a data absent reason must be present {value.exists() or dataAbsentReason.exists()}</t>
   </si>
   <si>
+    <t>1791: target not supported</t>
+  </si>
+  <si>
     <t>containment by OBX-4?</t>
   </si>
   <si>
@@ -2232,6 +2238,9 @@
   <si>
     <t>obs-6
 vs-3</t>
+  </si>
+  <si>
+    <t>1793: target not supported</t>
   </si>
   <si>
     <t>Observation.component.interpretation</t>
@@ -11418,7 +11427,7 @@
         <v>106</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>84</v>
+        <v>557</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>84</v>
@@ -11433,7 +11442,7 @@
         <v>137</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
@@ -11444,14 +11453,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -11473,16 +11482,16 @@
         <v>172</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
@@ -11510,10 +11519,10 @@
         <v>213</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>84</v>
@@ -11531,7 +11540,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11555,27 +11564,27 @@
         <v>84</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11598,19 +11607,19 @@
         <v>84</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>84</v>
@@ -11659,7 +11668,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11686,10 +11695,10 @@
         <v>84</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>
@@ -11700,10 +11709,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11729,13 +11738,13 @@
         <v>172</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11761,13 +11770,13 @@
         <v>84</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>84</v>
@@ -11785,7 +11794,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11809,27 +11818,27 @@
         <v>84</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11855,16 +11864,16 @@
         <v>172</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>84</v>
@@ -11893,7 +11902,7 @@
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>84</v>
@@ -11911,7 +11920,7 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -11926,7 +11935,7 @@
         <v>106</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>84</v>
@@ -11938,10 +11947,10 @@
         <v>84</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AQ74" t="s" s="2">
         <v>84</v>
@@ -11952,10 +11961,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11978,16 +11987,16 @@
         <v>84</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12037,7 +12046,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12061,27 +12070,27 @@
         <v>84</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR75" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12104,16 +12113,16 @@
         <v>84</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -12163,7 +12172,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12178,7 +12187,7 @@
         <v>106</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>84</v>
@@ -12187,27 +12196,27 @@
         <v>84</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR76" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12230,19 +12239,19 @@
         <v>84</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>84</v>
@@ -12291,7 +12300,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12303,7 +12312,7 @@
         <v>84</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>84</v>
@@ -12318,10 +12327,10 @@
         <v>84</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>84</v>
@@ -12332,10 +12341,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12456,10 +12465,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12582,14 +12591,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -12611,10 +12620,10 @@
         <v>139</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>183</v>
@@ -12669,7 +12678,7 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -12710,10 +12719,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12736,13 +12745,13 @@
         <v>84</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -12793,7 +12802,7 @@
         <v>84</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -12802,7 +12811,7 @@
         <v>94</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>106</v>
@@ -12820,10 +12829,10 @@
         <v>84</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AQ81" t="s" s="2">
         <v>84</v>
@@ -12834,10 +12843,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12860,13 +12869,13 @@
         <v>84</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12917,7 +12926,7 @@
         <v>84</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -12926,7 +12935,7 @@
         <v>94</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>106</v>
@@ -12944,10 +12953,10 @@
         <v>84</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>84</v>
@@ -12958,10 +12967,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12987,16 +12996,16 @@
         <v>172</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>84</v>
@@ -13024,10 +13033,10 @@
         <v>118</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>84</v>
@@ -13045,7 +13054,7 @@
         <v>84</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13069,13 +13078,13 @@
         <v>84</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AQ83" t="s" s="2">
         <v>84</v>
@@ -13086,10 +13095,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13115,16 +13124,16 @@
         <v>172</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>84</v>
@@ -13149,13 +13158,13 @@
         <v>84</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>84</v>
@@ -13173,7 +13182,7 @@
         <v>84</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13197,13 +13206,13 @@
         <v>84</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AQ84" t="s" s="2">
         <v>84</v>
@@ -13214,10 +13223,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13240,17 +13249,17 @@
         <v>84</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>84</v>
@@ -13299,7 +13308,7 @@
         <v>84</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -13329,7 +13338,7 @@
         <v>84</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AQ85" t="s" s="2">
         <v>84</v>
@@ -13340,10 +13349,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13369,10 +13378,10 @@
         <v>154</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -13423,7 +13432,7 @@
         <v>84</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
@@ -13450,10 +13459,10 @@
         <v>84</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>84</v>
@@ -13464,10 +13473,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13490,16 +13499,16 @@
         <v>95</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -13549,7 +13558,7 @@
         <v>84</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13576,10 +13585,10 @@
         <v>84</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>84</v>
@@ -13590,10 +13599,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13616,16 +13625,16 @@
         <v>95</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -13675,7 +13684,7 @@
         <v>84</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13702,10 +13711,10 @@
         <v>84</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AQ88" t="s" s="2">
         <v>84</v>
@@ -13716,10 +13725,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13742,19 +13751,19 @@
         <v>95</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>84</v>
@@ -13803,7 +13812,7 @@
         <v>84</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -13815,10 +13824,10 @@
         <v>84</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>84</v>
+        <v>690</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>84</v>
@@ -13830,10 +13839,10 @@
         <v>84</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>84</v>
@@ -13844,10 +13853,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13968,10 +13977,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14094,14 +14103,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -14123,10 +14132,10 @@
         <v>139</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="N92" t="s" s="2">
         <v>183</v>
@@ -14181,7 +14190,7 @@
         <v>84</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14222,10 +14231,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14251,16 +14260,16 @@
         <v>172</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>84</v>
@@ -14309,7 +14318,7 @@
         <v>84</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>94</v>
@@ -14333,7 +14342,7 @@
         <v>84</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>377</v>
@@ -14350,10 +14359,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14379,13 +14388,13 @@
         <v>455</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="O94" t="s" s="2">
         <v>459</v>
@@ -14437,7 +14446,7 @@
         <v>84</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14446,7 +14455,7 @@
         <v>94</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>106</v>
@@ -14461,7 +14470,7 @@
         <v>84</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>464</v>
@@ -14478,10 +14487,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14507,13 +14516,13 @@
         <v>172</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="O95" t="s" s="2">
         <v>553</v>
@@ -14565,7 +14574,7 @@
         <v>84</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14574,13 +14583,13 @@
         <v>94</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>84</v>
+        <v>713</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>84</v>
@@ -14595,7 +14604,7 @@
         <v>137</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AQ95" t="s" s="2">
         <v>84</v>
@@ -14606,14 +14615,14 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -14635,16 +14644,16 @@
         <v>172</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>84</v>
@@ -14672,10 +14681,10 @@
         <v>213</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>84</v>
@@ -14693,7 +14702,7 @@
         <v>84</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14717,27 +14726,27 @@
         <v>84</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AQ96" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR96" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14763,16 +14772,16 @@
         <v>85</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>84</v>
@@ -14821,7 +14830,7 @@
         <v>84</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>
@@ -14848,10 +14857,10 @@
         <v>84</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AQ97" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1747,7 +1747,7 @@
 vs-2</t>
   </si>
   <si>
-    <t>1792: target not supported</t>
+    <t>1793: target not supported</t>
   </si>
   <si>
     <t>value.nullFlavor</t>
@@ -2167,7 +2167,7 @@
 vs-3:If there is no a value a data absent reason must be present {value.exists() or dataAbsentReason.exists()}</t>
   </si>
   <si>
-    <t>1791: target not supported</t>
+    <t>1792: target not supported</t>
   </si>
   <si>
     <t>containment by OBX-4?</t>
@@ -2240,7 +2240,7 @@
 vs-3</t>
   </si>
   <si>
-    <t>1793: target not supported</t>
+    <t>1794: target not supported</t>
   </si>
   <si>
     <t>Observation.component.interpretation</t>

--- a/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file GMRV VITAL MEASUREMENT (#120.5) to us-core-vital-signs</t>
+    <t>This StructureDefinition contains the maps for VistA file GMRV VITAL MEASUREMENT (120.5) to us-core-vital-signs</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -571,7 +571,7 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t>866: terminologyMaps using VF_VitalsPosition on GMRV VITAL MEASUREMENT - QUALIFIER (#120.5-5)</t>
+    <t>866: terminologyMaps using VF_VitalsPosition on GMRV VITAL MEASUREMENT - QUALIFIER (120.5-5)</t>
   </si>
   <si>
     <t>Observation.modifierExtension</t>
@@ -739,7 +739,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>660: source value from GMRV VITAL MEASUREMENT - IEN (#120.5-.001)</t>
+    <t>660: source value from GMRV VITAL MEASUREMENT - IEN (120.5-.001)</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -871,7 +871,7 @@
     <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
   </si>
   <si>
-    <t>656: fixed value = #entered-in-error when GMRV VITAL MEASUREMENT - REASON ENTERED IN ERROR (#120.5-4) case not null</t>
+    <t>656: fixed value = #entered-in-error when GMRV VITAL MEASUREMENT - REASON ENTERED IN ERROR (120.5-4) case not null</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -1210,7 +1210,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFVitalsCodes</t>
   </si>
   <si>
-    <t>661: terminologyMaps using VF_VitalsCodes on GMRV VITAL MEASUREMENT - VITAL TYPE (#120.5-.03)</t>
+    <t>661: terminologyMaps using VF_VitalsCodes on GMRV VITAL MEASUREMENT - VITAL TYPE (120.5-.03)</t>
   </si>
   <si>
     <t>Observation.code.text</t>
@@ -1235,7 +1235,7 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
-    <t>659: reference from GMRV VITAL MEASUREMENT - PATIENT (#120.5-.02)</t>
+    <t>659: reference from GMRV VITAL MEASUREMENT - PATIENT (120.5-.02)</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1361,7 +1361,7 @@
 </t>
   </si>
   <si>
-    <t>657: source value from GMRV VITAL MEASUREMENT - DATE/TIME VITALS TAKEN (#120.5-.01)</t>
+    <t>657: source value from GMRV VITAL MEASUREMENT - DATE/TIME VITALS TAKEN (120.5-.01)</t>
   </si>
   <si>
     <t>Vital.VitalSign.VitalSignTakenDateTime,Vital.VitalSignQualifier.VitalSignTakenDateTime</t>
@@ -1383,7 +1383,7 @@
     <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
-    <t>652: source value from GMRV VITAL MEASUREMENT - DATE/TIME VITALS ENTERED (#120.5-.04)</t>
+    <t>652: source value from GMRV VITAL MEASUREMENT - DATE/TIME VITALS ENTERED (120.5-.04)</t>
   </si>
   <si>
     <t>Vital.VitalSign.VitalSignEnteredDateTime</t>
@@ -1414,7 +1414,7 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
-    <t>1653: reference from GMRV VITAL MEASUREMENT - HOSPITAL LOCATION (#120.5-.05)</t>
+    <t>1653: reference from GMRV VITAL MEASUREMENT - HOSPITAL LOCATION (120.5-.05)</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1517,7 +1517,7 @@
     <t>Quantity.value</t>
   </si>
   <si>
-    <t>664: source value from GMRV VITAL MEASUREMENT - RATE (#120.5-1.2) case VUID not = 4500634</t>
+    <t>664: source value from GMRV VITAL MEASUREMENT - RATE (120.5-1.2) case VUID not = 4500634</t>
   </si>
   <si>
     <t>Vital.VitalSign.Diastolic,Vital.VitalSign.Systolic,Vital.VitalSign.VitalResult,Vital.VitalSign.VitalResultNumeric</t>
@@ -1632,7 +1632,7 @@
     <t>Quantity.code</t>
   </si>
   <si>
-    <t>665: transform using VF_VitalsUnits on GMRV VITAL MEASUREMENT - VITAL TYPE (#120.5-.03)</t>
+    <t>665: transform using VF_VitalsUnits on GMRV VITAL MEASUREMENT - VITAL TYPE (120.5-.03)</t>
   </si>
   <si>
     <t>PQ.code, MO.currency, PQ.translation.code</t>
@@ -1867,7 +1867,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFVitalsMethod</t>
   </si>
   <si>
-    <t>867: terminologyMaps using VF_VitalsMethod on GMRV VITAL MEASUREMENT - QUALIFIER (#120.5-5)</t>
+    <t>867: terminologyMaps using VF_VitalsMethod on GMRV VITAL MEASUREMENT - QUALIFIER (120.5-5)</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1920,7 +1920,7 @@
     <t>Note that this is not meant to represent a device involved in the transmission of the result, e.g., a gateway.  Such devices may be documented using the Provenance resource where relevant.</t>
   </si>
   <si>
-    <t>1655: reference from GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (#120.5-5 &gt; 120.52-99.99)</t>
+    <t>1655: reference from GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
   </si>
   <si>
     <t>&lt; 49062001 |Device|</t>
@@ -2607,7 +2607,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="118.1171875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="116.58203125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="98.75" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$102</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3932" uniqueCount="718">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4133" uniqueCount="730">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -487,145 +487,149 @@
     <t>The position of the body when the observation was done, e.g. standing, sitting. To be used only when the body position in not precoordinated in the observation code.</t>
   </si>
   <si>
+    <t>Observation.extension:observation-bodyPosition.id</t>
+  </si>
+  <si>
+    <t>Observation.extension.id</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
-    <t>Observation.extension:observation-bodyPosition.id</t>
-  </si>
-  <si>
-    <t>Observation.extension.id</t>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Observation.extension:observation-bodyPosition.extension</t>
+  </si>
+  <si>
+    <t>Observation.extension.extension</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Observation.extension:observation-bodyPosition.url</t>
+  </si>
+  <si>
+    <t>Observation.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/observation-bodyPosition</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>Observation.extension:observation-bodyPosition.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFVitalsBodyPosition</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ext-1
+</t>
+  </si>
+  <si>
+    <t>1804: terminologyMaps using VF_VitalsBodyPosition on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
+  </si>
+  <si>
+    <t>Observation.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>DomainResource.modifierExtension</t>
+  </si>
+  <si>
+    <t>Observation.identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>Business Identifier for observation</t>
+  </si>
+  <si>
+    <t>A unique identifier assigned to this observation.</t>
+  </si>
+  <si>
+    <t>Allows observations to be distinguished and referenced.</t>
+  </si>
+  <si>
+    <t>Event.identifier</t>
+  </si>
+  <si>
+    <t>OBX.21  For OBX segments from systems without OBX-21 support a combination of ORC/OBR and OBX must be negotiated between trading partners to uniquely identify the OBX segment. Depending on how V2 has been implemented each of these may be an option: 1) OBR-3 + OBX-3 + OBX-4 or 2) OBR-3 + OBR-4 + OBX-3 + OBX-4 or 2) some other way to uniquely ID the OBR/ORC + OBX-3 + OBX-4.</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>Observation.identifier.id</t>
   </si>
   <si>
     <t xml:space="preserve">string
 </t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Observation.extension:observation-bodyPosition.extension</t>
-  </si>
-  <si>
-    <t>Observation.extension.extension</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Observation.extension:observation-bodyPosition.url</t>
-  </si>
-  <si>
-    <t>Observation.extension.url</t>
-  </si>
-  <si>
-    <t>identifies the meaning of the extension</t>
-  </si>
-  <si>
-    <t>Source of the definition for the extension code - a logical name or a URL.</t>
-  </si>
-  <si>
-    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/StructureDefinition/observation-bodyPosition</t>
-  </si>
-  <si>
-    <t>Extension.url</t>
-  </si>
-  <si>
-    <t>Observation.extension:observation-bodyPosition.value[x]</t>
-  </si>
-  <si>
-    <t>Observation.extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFVitalsPosition</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t>866: terminologyMaps using VF_VitalsPosition on GMRV VITAL MEASUREMENT - QUALIFIER (120.5-5)</t>
-  </si>
-  <si>
-    <t>Observation.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>DomainResource.modifierExtension</t>
-  </si>
-  <si>
-    <t>Observation.identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
-  </si>
-  <si>
-    <t>Business Identifier for observation</t>
-  </si>
-  <si>
-    <t>A unique identifier assigned to this observation.</t>
-  </si>
-  <si>
-    <t>Allows observations to be distinguished and referenced.</t>
-  </si>
-  <si>
-    <t>Event.identifier</t>
-  </si>
-  <si>
-    <t>OBX.21  For OBX segments from systems without OBX-21 support a combination of ORC/OBR and OBX must be negotiated between trading partners to uniquely identify the OBX segment. Depending on how V2 has been implemented each of these may be an option: 1) OBR-3 + OBX-3 + OBX-4 or 2) OBR-3 + OBR-4 + OBX-3 + OBX-4 or 2) some other way to uniquely ID the OBR/ORC + OBX-3 + OBX-4.</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>Observation.identifier.id</t>
   </si>
   <si>
     <t>Observation.identifier.extension</t>
@@ -1867,7 +1871,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFVitalsMethod</t>
   </si>
   <si>
-    <t>867: terminologyMaps using VF_VitalsMethod on GMRV VITAL MEASUREMENT - QUALIFIER (120.5-5)</t>
+    <t>867: terminologyMaps using VF_VitalsMethod on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1907,7 +1911,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/VitalSignsDevice)
+    <t xml:space="preserve">Reference(Device|DeviceMetric)
 </t>
   </si>
   <si>
@@ -1918,9 +1922,6 @@
   </si>
   <si>
     <t>Note that this is not meant to represent a device involved in the transmission of the result, e.g., a gateway.  Such devices may be documented using the Provenance resource where relevant.</t>
-  </si>
-  <si>
-    <t>1655: reference from GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
   </si>
   <si>
     <t>&lt; 49062001 |Device|</t>
@@ -2221,6 +2222,42 @@
   </si>
   <si>
     <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x]:valueCodeableConcept.id</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].id</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x]:valueCodeableConcept.extension</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].extension</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x]:valueCodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].coding</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFVitalsCuffSize</t>
+  </si>
+  <si>
+    <t>1805: terminologyMaps using VF_VitalsCuffSize on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x]:valueCodeableConcept.text</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].text</t>
   </si>
   <si>
     <t>Observation.component.dataAbsentReason</t>
@@ -2569,7 +2606,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR97"/>
+  <dimension ref="A1:AR102"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="91.8671875" customWidth="true" bestFit="true"/>
@@ -2607,7 +2644,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="116.58203125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="144.703125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="98.75" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
@@ -3849,7 +3886,7 @@
         <v>83</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>151</v>
+        <v>84</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>145</v>
@@ -3881,10 +3918,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3907,13 +3944,13 @@
         <v>84</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -3964,7 +4001,7 @@
         <v>84</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>82</v>
@@ -3973,7 +4010,7 @@
         <v>94</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>84</v>
+        <v>156</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>84</v>
@@ -3994,7 +4031,7 @@
         <v>84</v>
       </c>
       <c r="AP11" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AQ11" t="s" s="2">
         <v>84</v>
@@ -4005,10 +4042,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -4079,7 +4116,7 @@
         <v>142</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>84</v>
@@ -4088,7 +4125,7 @@
         <v>143</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>82</v>
@@ -4129,10 +4166,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="B13" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -4158,13 +4195,13 @@
         <v>108</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -4172,49 +4209,49 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="S13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="S13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>169</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>94</v>
@@ -4255,10 +4292,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4281,13 +4318,13 @@
         <v>84</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -4314,29 +4351,29 @@
         <v>84</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF14" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>82</v>
@@ -4345,7 +4382,7 @@
         <v>94</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>84</v>
+        <v>177</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>106</v>
@@ -4657,13 +4694,13 @@
         <v>84</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="L17" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4714,7 +4751,7 @@
         <v>84</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>82</v>
@@ -4744,7 +4781,7 @@
         <v>84</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AQ17" t="s" s="2">
         <v>84</v>
@@ -4755,10 +4792,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4784,10 +4821,10 @@
         <v>139</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>183</v>
@@ -4831,7 +4868,7 @@
         <v>142</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>84</v>
@@ -4840,7 +4877,7 @@
         <v>143</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -4870,7 +4907,7 @@
         <v>84</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AQ18" t="s" s="2">
         <v>84</v>
@@ -4881,10 +4918,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4910,16 +4947,16 @@
         <v>114</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>84</v>
@@ -4944,13 +4981,13 @@
         <v>84</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>84</v>
@@ -4968,7 +5005,7 @@
         <v>84</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -4998,7 +5035,7 @@
         <v>137</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>84</v>
@@ -5009,10 +5046,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -5035,19 +5072,19 @@
         <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>84</v>
@@ -5072,13 +5109,13 @@
         <v>84</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>84</v>
@@ -5096,7 +5133,7 @@
         <v>84</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -5123,10 +5160,10 @@
         <v>84</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>84</v>
@@ -5137,10 +5174,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5166,16 +5203,16 @@
         <v>108</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>84</v>
@@ -5188,7 +5225,7 @@
         <v>84</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="U21" t="s" s="2">
         <v>84</v>
@@ -5224,7 +5261,7 @@
         <v>84</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -5251,10 +5288,10 @@
         <v>84</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AQ21" t="s" s="2">
         <v>84</v>
@@ -5265,10 +5302,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5291,16 +5328,16 @@
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>154</v>
+        <v>196</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -5314,7 +5351,7 @@
         <v>84</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="U22" t="s" s="2">
         <v>84</v>
@@ -5350,7 +5387,7 @@
         <v>84</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
@@ -5365,7 +5402,7 @@
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>84</v>
@@ -5377,10 +5414,10 @@
         <v>84</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AQ22" t="s" s="2">
         <v>84</v>
@@ -5391,10 +5428,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5417,13 +5454,13 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -5474,7 +5511,7 @@
         <v>84</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -5501,10 +5538,10 @@
         <v>84</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AQ23" t="s" s="2">
         <v>84</v>
@@ -5515,10 +5552,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5541,16 +5578,16 @@
         <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5600,7 +5637,7 @@
         <v>84</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -5627,10 +5664,10 @@
         <v>84</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AQ24" t="s" s="2">
         <v>84</v>
@@ -5641,14 +5678,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5667,17 +5704,17 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>84</v>
@@ -5726,7 +5763,7 @@
         <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -5747,16 +5784,16 @@
         <v>84</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AQ25" t="s" s="2">
         <v>84</v>
@@ -5767,14 +5804,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5793,16 +5830,16 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5852,7 +5889,7 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5873,16 +5910,16 @@
         <v>84</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>84</v>
@@ -5893,10 +5930,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5922,16 +5959,16 @@
         <v>114</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>84</v>
@@ -5956,11 +5993,11 @@
         <v>84</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>84</v>
@@ -5978,7 +6015,7 @@
         <v>84</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>94</v>
@@ -5993,25 +6030,25 @@
         <v>106</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AR27" t="s" s="2">
         <v>84</v>
@@ -6019,10 +6056,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6045,19 +6082,19 @@
         <v>84</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -6067,7 +6104,7 @@
         <v>84</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>84</v>
@@ -6085,16 +6122,16 @@
         <v>118</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AC28" s="2"/>
       <c r="AD28" t="s" s="2">
@@ -6104,7 +6141,7 @@
         <v>143</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -6119,7 +6156,7 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>84</v>
@@ -6134,10 +6171,10 @@
         <v>84</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>84</v>
@@ -6145,13 +6182,13 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>84</v>
@@ -6173,19 +6210,19 @@
         <v>84</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -6213,10 +6250,10 @@
         <v>118</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>84</v>
@@ -6234,7 +6271,7 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -6264,10 +6301,10 @@
         <v>84</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AR29" t="s" s="2">
         <v>84</v>
@@ -6275,10 +6312,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6301,13 +6338,13 @@
         <v>84</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6358,7 +6395,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -6388,7 +6425,7 @@
         <v>84</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>84</v>
@@ -6399,10 +6436,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6428,10 +6465,10 @@
         <v>139</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N31" t="s" s="2">
         <v>183</v>
@@ -6475,7 +6512,7 @@
         <v>142</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>84</v>
@@ -6484,7 +6521,7 @@
         <v>143</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6514,7 +6551,7 @@
         <v>84</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>84</v>
@@ -6525,10 +6562,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6551,19 +6588,19 @@
         <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -6612,7 +6649,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6639,10 +6676,10 @@
         <v>84</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>84</v>
@@ -6653,10 +6690,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6679,13 +6716,13 @@
         <v>84</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6736,7 +6773,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6766,7 +6803,7 @@
         <v>84</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
@@ -6777,10 +6814,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6806,10 +6843,10 @@
         <v>139</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>183</v>
@@ -6853,7 +6890,7 @@
         <v>142</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>84</v>
@@ -6862,7 +6899,7 @@
         <v>143</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6892,7 +6929,7 @@
         <v>84</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
@@ -6903,10 +6940,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6932,23 +6969,23 @@
         <v>108</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>84</v>
@@ -6990,7 +7027,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -7017,10 +7054,10 @@
         <v>84</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
@@ -7031,10 +7068,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7057,16 +7094,16 @@
         <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>154</v>
+        <v>196</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -7116,7 +7153,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -7143,10 +7180,10 @@
         <v>84</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
@@ -7157,10 +7194,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7186,21 +7223,21 @@
         <v>114</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>84</v>
@@ -7242,7 +7279,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -7269,10 +7306,10 @@
         <v>84</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
@@ -7283,10 +7320,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7309,17 +7346,17 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>154</v>
+        <v>196</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
@@ -7368,7 +7405,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7395,10 +7432,10 @@
         <v>84</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
@@ -7409,10 +7446,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7435,19 +7472,19 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -7496,7 +7533,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7523,10 +7560,10 @@
         <v>84</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -7537,10 +7574,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7563,19 +7600,19 @@
         <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>154</v>
+        <v>196</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7624,7 +7661,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7651,10 +7688,10 @@
         <v>84</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
@@ -7665,14 +7702,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7691,19 +7728,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7728,13 +7765,13 @@
         <v>84</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>84</v>
@@ -7752,7 +7789,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>94</v>
@@ -7773,30 +7810,30 @@
         <v>84</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7819,13 +7856,13 @@
         <v>84</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7876,7 +7913,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7906,7 +7943,7 @@
         <v>84</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -7917,10 +7954,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7946,10 +7983,10 @@
         <v>139</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>183</v>
@@ -7993,7 +8030,7 @@
         <v>142</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>84</v>
@@ -8002,7 +8039,7 @@
         <v>143</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -8032,7 +8069,7 @@
         <v>84</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
@@ -8043,10 +8080,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8069,19 +8106,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -8106,11 +8143,11 @@
         <v>84</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>84</v>
@@ -8128,7 +8165,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -8143,7 +8180,7 @@
         <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>84</v>
@@ -8155,10 +8192,10 @@
         <v>84</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -8169,10 +8206,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8195,19 +8232,19 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>154</v>
+        <v>196</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -8256,7 +8293,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8283,10 +8320,10 @@
         <v>84</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -8297,10 +8334,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8323,19 +8360,19 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -8384,7 +8421,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8399,25 +8436,25 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>84</v>
@@ -8425,10 +8462,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8451,16 +8488,16 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8510,7 +8547,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8537,13 +8574,13 @@
         <v>84</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>84</v>
@@ -8551,14 +8588,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -8577,19 +8614,19 @@
         <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
@@ -8638,7 +8675,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8659,19 +8696,19 @@
         <v>84</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>84</v>
@@ -8679,14 +8716,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -8705,19 +8742,19 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
@@ -8754,7 +8791,7 @@
         <v>84</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AC49" s="2"/>
       <c r="AD49" t="s" s="2">
@@ -8764,7 +8801,7 @@
         <v>143</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8773,10 +8810,10 @@
         <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>84</v>
@@ -8785,19 +8822,19 @@
         <v>84</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>84</v>
@@ -8805,16 +8842,16 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8833,19 +8870,19 @@
         <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8894,7 +8931,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8903,31 +8940,31 @@
         <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>84</v>
@@ -8935,10 +8972,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8961,16 +8998,16 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -9020,7 +9057,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -9035,10 +9072,10 @@
         <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>84</v>
@@ -9047,13 +9084,13 @@
         <v>84</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>84</v>
@@ -9061,10 +9098,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9087,17 +9124,17 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -9146,7 +9183,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9161,25 +9198,25 @@
         <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>84</v>
@@ -9187,10 +9224,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9213,19 +9250,19 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>84</v>
@@ -9250,19 +9287,19 @@
         <v>84</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AC53" s="2"/>
       <c r="AD53" t="s" s="2">
@@ -9272,7 +9309,7 @@
         <v>143</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -9281,7 +9318,7 @@
         <v>94</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>106</v>
@@ -9296,30 +9333,30 @@
         <v>84</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR53" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>84</v>
@@ -9341,19 +9378,19 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>84</v>
@@ -9378,13 +9415,13 @@
         <v>84</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>84</v>
@@ -9402,7 +9439,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9411,7 +9448,7 @@
         <v>94</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>106</v>
@@ -9426,27 +9463,27 @@
         <v>84</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR54" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9469,13 +9506,13 @@
         <v>84</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -9526,7 +9563,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9556,7 +9593,7 @@
         <v>84</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9567,10 +9604,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9596,10 +9633,10 @@
         <v>139</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>183</v>
@@ -9643,7 +9680,7 @@
         <v>142</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>84</v>
@@ -9652,7 +9689,7 @@
         <v>143</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9682,7 +9719,7 @@
         <v>84</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9693,10 +9730,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9719,19 +9756,19 @@
         <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>84</v>
@@ -9780,7 +9817,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9795,10 +9832,10 @@
         <v>106</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>84</v>
@@ -9807,10 +9844,10 @@
         <v>84</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9821,10 +9858,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9850,20 +9887,20 @@
         <v>114</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q58" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="R58" t="s" s="2">
         <v>84</v>
@@ -9884,13 +9921,13 @@
         <v>84</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
@@ -9908,7 +9945,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9935,10 +9972,10 @@
         <v>84</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9949,10 +9986,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9975,17 +10012,17 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>154</v>
+        <v>196</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -10034,7 +10071,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10061,10 +10098,10 @@
         <v>84</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -10075,10 +10112,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10104,14 +10141,14 @@
         <v>108</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -10160,7 +10197,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10169,7 +10206,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -10187,10 +10224,10 @@
         <v>84</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -10201,10 +10238,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10230,16 +10267,16 @@
         <v>114</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
@@ -10288,7 +10325,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -10303,7 +10340,7 @@
         <v>106</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>84</v>
@@ -10315,10 +10352,10 @@
         <v>84</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -10329,10 +10366,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10355,13 +10392,13 @@
         <v>84</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>154</v>
+        <v>196</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10412,7 +10449,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10453,10 +10490,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10534,7 +10571,7 @@
         <v>143</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10575,13 +10612,13 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="B64" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="B64" t="s" s="2">
-        <v>527</v>
-      </c>
       <c r="C64" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>84</v>
@@ -10603,16 +10640,16 @@
         <v>84</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10662,7 +10699,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10671,7 +10708,7 @@
         <v>83</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>151</v>
+        <v>84</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>145</v>
@@ -10703,10 +10740,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10729,13 +10766,13 @@
         <v>84</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10786,7 +10823,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -10795,7 +10832,7 @@
         <v>94</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>84</v>
+        <v>156</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>84</v>
@@ -10816,7 +10853,7 @@
         <v>84</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
@@ -10827,10 +10864,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10901,7 +10938,7 @@
         <v>142</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>84</v>
@@ -10910,7 +10947,7 @@
         <v>143</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10951,10 +10988,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10980,13 +11017,13 @@
         <v>108</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10994,7 +11031,7 @@
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="S67" t="s" s="2">
         <v>84</v>
@@ -11036,7 +11073,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>94</v>
@@ -11077,10 +11114,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11103,13 +11140,13 @@
         <v>84</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -11121,7 +11158,7 @@
         <v>84</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>84</v>
@@ -11160,7 +11197,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -11169,7 +11206,7 @@
         <v>94</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>84</v>
+        <v>177</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>106</v>
@@ -11201,10 +11238,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11227,13 +11264,13 @@
         <v>84</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>154</v>
+        <v>196</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -11284,7 +11321,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11325,10 +11362,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11351,19 +11388,19 @@
         <v>84</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>84</v>
@@ -11388,13 +11425,13 @@
         <v>84</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>84</v>
@@ -11412,7 +11449,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11421,13 +11458,13 @@
         <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>84</v>
@@ -11442,7 +11479,7 @@
         <v>137</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
@@ -11453,14 +11490,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -11479,19 +11516,19 @@
         <v>84</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
@@ -11516,13 +11553,13 @@
         <v>84</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>84</v>
@@ -11540,7 +11577,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11564,27 +11601,27 @@
         <v>84</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11607,19 +11644,19 @@
         <v>84</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>84</v>
@@ -11668,7 +11705,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11695,10 +11732,10 @@
         <v>84</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>
@@ -11709,10 +11746,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11735,16 +11772,16 @@
         <v>84</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11770,13 +11807,13 @@
         <v>84</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>84</v>
@@ -11794,7 +11831,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11818,27 +11855,27 @@
         <v>84</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11861,19 +11898,19 @@
         <v>84</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>84</v>
@@ -11898,11 +11935,11 @@
         <v>84</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>84</v>
@@ -11920,7 +11957,7 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -11935,7 +11972,7 @@
         <v>106</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>84</v>
@@ -11947,10 +11984,10 @@
         <v>84</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AQ74" t="s" s="2">
         <v>84</v>
@@ -11961,10 +11998,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11987,16 +12024,16 @@
         <v>84</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12046,7 +12083,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12070,27 +12107,27 @@
         <v>84</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR75" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12104,7 +12141,7 @@
         <v>94</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>84</v>
@@ -12113,16 +12150,16 @@
         <v>84</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -12172,7 +12209,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12187,7 +12224,7 @@
         <v>106</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>613</v>
+        <v>84</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>84</v>
@@ -12367,13 +12404,13 @@
         <v>84</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -12424,7 +12461,7 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12454,7 +12491,7 @@
         <v>84</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>84</v>
@@ -12494,10 +12531,10 @@
         <v>139</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N79" t="s" s="2">
         <v>183</v>
@@ -12550,7 +12587,7 @@
         <v>84</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12580,7 +12617,7 @@
         <v>84</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>84</v>
@@ -12993,7 +13030,7 @@
         <v>84</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L83" t="s" s="2">
         <v>646</v>
@@ -13084,7 +13121,7 @@
         <v>653</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AQ83" t="s" s="2">
         <v>84</v>
@@ -13121,7 +13158,7 @@
         <v>84</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L84" t="s" s="2">
         <v>655</v>
@@ -13158,7 +13195,7 @@
         <v>84</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Y84" t="s" s="2">
         <v>659</v>
@@ -13212,7 +13249,7 @@
         <v>653</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AQ84" t="s" s="2">
         <v>84</v>
@@ -13375,7 +13412,7 @@
         <v>84</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>154</v>
+        <v>196</v>
       </c>
       <c r="L86" t="s" s="2">
         <v>668</v>
@@ -13879,13 +13916,13 @@
         <v>84</v>
       </c>
       <c r="K90" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="L90" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -13936,7 +13973,7 @@
         <v>84</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -13966,7 +14003,7 @@
         <v>84</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AQ90" t="s" s="2">
         <v>84</v>
@@ -14006,10 +14043,10 @@
         <v>139</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>183</v>
@@ -14062,7 +14099,7 @@
         <v>84</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -14092,7 +14129,7 @@
         <v>84</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AQ91" t="s" s="2">
         <v>84</v>
@@ -14257,7 +14294,7 @@
         <v>95</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L93" t="s" s="2">
         <v>697</v>
@@ -14294,13 +14331,13 @@
         <v>84</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>84</v>
@@ -14345,13 +14382,13 @@
         <v>701</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AQ93" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AR93" t="s" s="2">
         <v>84</v>
@@ -14385,7 +14422,7 @@
         <v>95</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L94" t="s" s="2">
         <v>703</v>
@@ -14397,7 +14434,7 @@
         <v>705</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>84</v>
@@ -14422,28 +14459,26 @@
         <v>84</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="AC94" s="2"/>
       <c r="AD94" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>84</v>
+        <v>143</v>
       </c>
       <c r="AF94" t="s" s="2">
         <v>702</v>
@@ -14473,16 +14508,16 @@
         <v>707</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AQ94" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR94" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="95" hidden="true">
@@ -14490,9 +14525,11 @@
         <v>708</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="C95" s="2"/>
+        <v>702</v>
+      </c>
+      <c r="C95" t="s" s="2">
+        <v>709</v>
+      </c>
       <c r="D95" t="s" s="2">
         <v>84</v>
       </c>
@@ -14510,22 +14547,22 @@
         <v>84</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>553</v>
+        <v>460</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>84</v>
@@ -14550,13 +14587,13 @@
         <v>84</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>554</v>
+        <v>461</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>555</v>
+        <v>462</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>84</v>
@@ -14574,7 +14611,7 @@
         <v>84</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14583,13 +14620,13 @@
         <v>94</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>713</v>
+        <v>84</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>84</v>
@@ -14598,38 +14635,38 @@
         <v>84</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>84</v>
+        <v>707</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>137</v>
+        <v>465</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>558</v>
+        <v>466</v>
       </c>
       <c r="AQ95" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR95" t="s" s="2">
-        <v>84</v>
+        <v>467</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>560</v>
+        <v>84</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>84</v>
@@ -14641,20 +14678,16 @@
         <v>84</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>172</v>
+        <v>196</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>561</v>
+        <v>153</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>564</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>84</v>
       </c>
@@ -14678,13 +14711,13 @@
         <v>84</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>213</v>
+        <v>84</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>565</v>
+        <v>84</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>566</v>
+        <v>84</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>84</v>
@@ -14702,19 +14735,19 @@
         <v>84</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>714</v>
+        <v>155</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>84</v>
@@ -14726,31 +14759,31 @@
         <v>84</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>567</v>
+        <v>84</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>568</v>
+        <v>84</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>569</v>
+        <v>157</v>
       </c>
       <c r="AQ96" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR96" t="s" s="2">
-        <v>570</v>
+        <v>84</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -14769,20 +14802,18 @@
         <v>84</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>85</v>
+        <v>139</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>716</v>
+        <v>198</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>717</v>
+        <v>199</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>623</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>84</v>
       </c>
@@ -14818,19 +14849,19 @@
         <v>84</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>84</v>
+        <v>160</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>84</v>
+        <v>143</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>715</v>
+        <v>161</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>
@@ -14842,35 +14873,673 @@
         <v>84</v>
       </c>
       <c r="AJ97" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP97" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR97" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="P98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Y98" s="2"/>
+      <c r="Z98" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="AK97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO97" t="s" s="2">
+      <c r="AK98" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AP98" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AQ98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR98" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="99" hidden="true">
+      <c r="A99" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="P99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AP99" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AQ99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR99" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="100" hidden="true">
+      <c r="A100" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="P100" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO100" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AP100" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AQ100" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR100" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="101" hidden="true">
+      <c r="A101" t="s" s="2">
+        <v>726</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>726</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="P101" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>726</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AP101" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AQ101" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR101" t="s" s="2">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="102" hidden="true">
+      <c r="A102" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="O102" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="P102" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO102" t="s" s="2">
         <v>625</v>
       </c>
-      <c r="AP97" t="s" s="2">
+      <c r="AP102" t="s" s="2">
         <v>626</v>
       </c>
-      <c r="AQ97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR97" t="s" s="2">
+      <c r="AQ102" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR102" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR97">
+  <autoFilter ref="A1:AR102">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -14880,7 +15549,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI96">
+  <conditionalFormatting sqref="A2:AI101">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4133" uniqueCount="730">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4133" uniqueCount="733">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1217,6 +1217,9 @@
     <t>661: terminologyMaps using VF_VitalsCodes on GMRV VITAL MEASUREMENT - VITAL TYPE (120.5-.03)</t>
   </si>
   <si>
+    <t>Vital.VitalSign.VitalTypeIEN</t>
+  </si>
+  <si>
     <t>Observation.code.text</t>
   </si>
   <si>
@@ -1242,6 +1245,9 @@
     <t>659: reference from GMRV VITAL MEASUREMENT - PATIENT (120.5-.02)</t>
   </si>
   <si>
+    <t>Vital.VitalSign.PatientIEN</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -1419,6 +1425,9 @@
   </si>
   <si>
     <t>1653: reference from GMRV VITAL MEASUREMENT - HOSPITAL LOCATION (120.5-.05)</t>
+  </si>
+  <si>
+    <t>Vital.VitalSign.LocationIEN</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -8183,7 +8192,7 @@
         <v>386</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>84</v>
+        <v>387</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>84</v>
@@ -8206,10 +8215,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8334,10 +8343,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8360,19 +8369,19 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -8421,7 +8430,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8436,25 +8445,25 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>84</v>
+        <v>396</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>84</v>
@@ -8462,10 +8471,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8488,16 +8497,16 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8547,7 +8556,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8577,10 +8586,10 @@
         <v>378</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>84</v>
@@ -8588,14 +8597,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -8614,19 +8623,19 @@
         <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
@@ -8675,7 +8684,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8696,19 +8705,19 @@
         <v>84</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>84</v>
@@ -8716,14 +8725,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -8742,19 +8751,19 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
@@ -8791,7 +8800,7 @@
         <v>84</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AC49" s="2"/>
       <c r="AD49" t="s" s="2">
@@ -8801,7 +8810,7 @@
         <v>143</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8810,10 +8819,10 @@
         <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>84</v>
@@ -8822,19 +8831,19 @@
         <v>84</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>84</v>
@@ -8842,16 +8851,16 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8870,19 +8879,19 @@
         <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8931,7 +8940,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8940,31 +8949,31 @@
         <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>84</v>
@@ -8972,10 +8981,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8998,16 +9007,16 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -9057,7 +9066,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -9072,10 +9081,10 @@
         <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>84</v>
@@ -9084,13 +9093,13 @@
         <v>84</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>84</v>
@@ -9098,10 +9107,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9124,17 +9133,17 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -9183,7 +9192,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9198,25 +9207,25 @@
         <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>84</v>
+        <v>453</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>84</v>
@@ -9224,10 +9233,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9250,19 +9259,19 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>84</v>
@@ -9290,16 +9299,16 @@
         <v>214</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AC53" s="2"/>
       <c r="AD53" t="s" s="2">
@@ -9309,7 +9318,7 @@
         <v>143</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -9318,7 +9327,7 @@
         <v>94</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>106</v>
@@ -9333,30 +9342,30 @@
         <v>84</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR53" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>84</v>
@@ -9378,19 +9387,19 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>84</v>
@@ -9418,10 +9427,10 @@
         <v>214</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>84</v>
@@ -9439,7 +9448,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9448,7 +9457,7 @@
         <v>94</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>106</v>
@@ -9463,27 +9472,27 @@
         <v>84</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR54" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9604,10 +9613,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9730,10 +9739,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9756,19 +9765,19 @@
         <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>84</v>
@@ -9817,7 +9826,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9832,10 +9841,10 @@
         <v>106</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>84</v>
@@ -9844,10 +9853,10 @@
         <v>84</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9858,10 +9867,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9887,20 +9896,20 @@
         <v>114</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q58" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="R58" t="s" s="2">
         <v>84</v>
@@ -9924,10 +9933,10 @@
         <v>174</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
@@ -9945,7 +9954,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9972,10 +9981,10 @@
         <v>84</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9986,10 +9995,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10015,14 +10024,14 @@
         <v>196</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -10071,7 +10080,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10098,10 +10107,10 @@
         <v>84</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -10112,10 +10121,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10141,14 +10150,14 @@
         <v>108</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -10197,7 +10206,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10206,7 +10215,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -10224,10 +10233,10 @@
         <v>84</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -10238,10 +10247,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10267,16 +10276,16 @@
         <v>114</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
@@ -10325,7 +10334,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -10340,10 +10349,10 @@
         <v>106</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>84</v>
+        <v>387</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>84</v>
@@ -10352,10 +10361,10 @@
         <v>84</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -10366,10 +10375,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10395,10 +10404,10 @@
         <v>196</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10490,10 +10499,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10612,13 +10621,13 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>84</v>
@@ -10640,16 +10649,16 @@
         <v>84</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10740,10 +10749,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10864,10 +10873,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10988,10 +10997,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11031,7 +11040,7 @@
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="S67" t="s" s="2">
         <v>84</v>
@@ -11114,10 +11123,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11140,7 +11149,7 @@
         <v>84</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="L68" t="s" s="2">
         <v>172</v>
@@ -11158,7 +11167,7 @@
         <v>84</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>84</v>
@@ -11238,10 +11247,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11267,10 +11276,10 @@
         <v>196</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -11321,7 +11330,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11362,10 +11371,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11391,16 +11400,16 @@
         <v>171</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>84</v>
@@ -11428,10 +11437,10 @@
         <v>214</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>84</v>
@@ -11449,7 +11458,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11458,13 +11467,13 @@
         <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>84</v>
@@ -11479,7 +11488,7 @@
         <v>137</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
@@ -11490,14 +11499,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -11519,16 +11528,16 @@
         <v>171</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
@@ -11556,10 +11565,10 @@
         <v>214</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>84</v>
@@ -11577,7 +11586,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11601,27 +11610,27 @@
         <v>84</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11644,19 +11653,19 @@
         <v>84</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>84</v>
@@ -11705,7 +11714,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11732,10 +11741,10 @@
         <v>84</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>
@@ -11746,10 +11755,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11775,13 +11784,13 @@
         <v>171</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11807,13 +11816,13 @@
         <v>84</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>84</v>
@@ -11831,7 +11840,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11855,27 +11864,27 @@
         <v>84</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11901,16 +11910,16 @@
         <v>171</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>84</v>
@@ -11939,7 +11948,7 @@
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>84</v>
@@ -11957,7 +11966,7 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -11972,7 +11981,7 @@
         <v>106</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>84</v>
@@ -11984,10 +11993,10 @@
         <v>84</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="AQ74" t="s" s="2">
         <v>84</v>
@@ -11998,10 +12007,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12024,16 +12033,16 @@
         <v>84</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12083,7 +12092,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12107,27 +12116,27 @@
         <v>84</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR75" t="s" s="2">
-        <v>608</v>
+        <v>611</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12150,16 +12159,16 @@
         <v>84</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -12209,7 +12218,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12233,27 +12242,27 @@
         <v>84</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR76" t="s" s="2">
-        <v>617</v>
+        <v>620</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12276,19 +12285,19 @@
         <v>84</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>84</v>
@@ -12337,7 +12346,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12349,7 +12358,7 @@
         <v>84</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>84</v>
@@ -12364,10 +12373,10 @@
         <v>84</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>84</v>
@@ -12378,10 +12387,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12502,10 +12511,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12628,14 +12637,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -12657,10 +12666,10 @@
         <v>139</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>183</v>
@@ -12715,7 +12724,7 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -12756,10 +12765,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12782,13 +12791,13 @@
         <v>84</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -12839,7 +12848,7 @@
         <v>84</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -12848,7 +12857,7 @@
         <v>94</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>106</v>
@@ -12866,10 +12875,10 @@
         <v>84</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="AQ81" t="s" s="2">
         <v>84</v>
@@ -12880,10 +12889,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12906,13 +12915,13 @@
         <v>84</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12963,7 +12972,7 @@
         <v>84</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -12972,7 +12981,7 @@
         <v>94</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>106</v>
@@ -12990,10 +12999,10 @@
         <v>84</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>84</v>
@@ -13004,10 +13013,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13033,16 +13042,16 @@
         <v>171</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>84</v>
@@ -13070,10 +13079,10 @@
         <v>118</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>84</v>
@@ -13091,7 +13100,7 @@
         <v>84</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13115,13 +13124,13 @@
         <v>84</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="AQ83" t="s" s="2">
         <v>84</v>
@@ -13132,10 +13141,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13161,16 +13170,16 @@
         <v>171</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>84</v>
@@ -13195,13 +13204,13 @@
         <v>84</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>84</v>
@@ -13219,7 +13228,7 @@
         <v>84</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13243,13 +13252,13 @@
         <v>84</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="AQ84" t="s" s="2">
         <v>84</v>
@@ -13260,10 +13269,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13286,17 +13295,17 @@
         <v>84</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>84</v>
@@ -13345,7 +13354,7 @@
         <v>84</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -13375,7 +13384,7 @@
         <v>84</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="AQ85" t="s" s="2">
         <v>84</v>
@@ -13386,10 +13395,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13415,10 +13424,10 @@
         <v>196</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -13469,7 +13478,7 @@
         <v>84</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
@@ -13496,10 +13505,10 @@
         <v>84</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>84</v>
@@ -13510,10 +13519,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13536,16 +13545,16 @@
         <v>95</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -13595,7 +13604,7 @@
         <v>84</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13622,10 +13631,10 @@
         <v>84</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>84</v>
@@ -13636,10 +13645,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13662,16 +13671,16 @@
         <v>95</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -13721,7 +13730,7 @@
         <v>84</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13748,10 +13757,10 @@
         <v>84</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="AQ88" t="s" s="2">
         <v>84</v>
@@ -13762,10 +13771,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13788,19 +13797,19 @@
         <v>95</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>84</v>
@@ -13849,7 +13858,7 @@
         <v>84</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -13861,10 +13870,10 @@
         <v>84</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>84</v>
@@ -13876,10 +13885,10 @@
         <v>84</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>84</v>
@@ -13890,10 +13899,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14014,10 +14023,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14140,14 +14149,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -14169,10 +14178,10 @@
         <v>139</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="N92" t="s" s="2">
         <v>183</v>
@@ -14227,7 +14236,7 @@
         <v>84</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14268,10 +14277,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14297,16 +14306,16 @@
         <v>171</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>84</v>
@@ -14355,7 +14364,7 @@
         <v>84</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>94</v>
@@ -14379,7 +14388,7 @@
         <v>84</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>378</v>
@@ -14396,10 +14405,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14422,19 +14431,19 @@
         <v>95</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>84</v>
@@ -14462,16 +14471,16 @@
         <v>214</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AC94" s="2"/>
       <c r="AD94" t="s" s="2">
@@ -14481,7 +14490,7 @@
         <v>143</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14490,7 +14499,7 @@
         <v>94</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>106</v>
@@ -14505,30 +14514,30 @@
         <v>84</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="AQ94" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR94" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="D95" t="s" s="2">
         <v>84</v>
@@ -14553,16 +14562,16 @@
         <v>171</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>84</v>
@@ -14590,10 +14599,10 @@
         <v>214</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>84</v>
@@ -14611,7 +14620,7 @@
         <v>84</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14620,7 +14629,7 @@
         <v>94</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>106</v>
@@ -14635,27 +14644,27 @@
         <v>84</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="AQ95" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR95" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14776,10 +14785,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14902,10 +14911,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14969,7 +14978,7 @@
       </c>
       <c r="Y98" s="2"/>
       <c r="Z98" t="s" s="2">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>84</v>
@@ -15002,7 +15011,7 @@
         <v>106</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="AL98" t="s" s="2">
         <v>84</v>
@@ -15028,10 +15037,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15156,10 +15165,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15185,16 +15194,16 @@
         <v>171</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>84</v>
@@ -15222,10 +15231,10 @@
         <v>214</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>84</v>
@@ -15243,7 +15252,7 @@
         <v>84</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>82</v>
@@ -15252,13 +15261,13 @@
         <v>94</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>84</v>
@@ -15273,7 +15282,7 @@
         <v>137</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="AQ100" t="s" s="2">
         <v>84</v>
@@ -15284,14 +15293,14 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -15313,16 +15322,16 @@
         <v>171</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>84</v>
@@ -15350,10 +15359,10 @@
         <v>214</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>84</v>
@@ -15371,7 +15380,7 @@
         <v>84</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15395,27 +15404,27 @@
         <v>84</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="AQ101" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15441,16 +15450,16 @@
         <v>85</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>84</v>
@@ -15499,7 +15508,7 @@
         <v>84</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15526,10 +15535,10 @@
         <v>84</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="AQ102" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$139</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4133" uniqueCount="733">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5635" uniqueCount="778">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2173,6 +2173,10 @@
     <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
   </si>
   <si>
+    <t xml:space="preserve">pattern:code}
+</t>
+  </si>
+  <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 vs-3:If there is no a value a data absent reason must be present {value.exists() or dataAbsentReason.exists()}</t>
   </si>
@@ -2233,42 +2237,6 @@
     <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
   </si>
   <si>
-    <t>Observation.component.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueCodeableConcept.id</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].id</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueCodeableConcept.extension</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].extension</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueCodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].coding</t>
-  </si>
-  <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFVitalsCuffSize</t>
-  </si>
-  <si>
-    <t>1805: terminologyMaps using VF_VitalsCuffSize on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueCodeableConcept.text</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].text</t>
-  </si>
-  <si>
     <t>Observation.component.dataAbsentReason</t>
   </si>
   <si>
@@ -2299,6 +2267,174 @@
   </si>
   <si>
     <t>Guidance on how to interpret the value by comparison to a normal or recommended range.</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition</t>
+  </si>
+  <si>
+    <t>va-pre-condition</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.id</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.modifierExtension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.code</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.value[x]:valueCodeableConcept.id</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].id</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.value[x]:valueCodeableConcept.extension</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].extension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.value[x]:valueCodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].coding</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFVitalsPrecondition</t>
+  </si>
+  <si>
+    <t>1802: terminologyMaps using VF_VitalsPrecondition on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.value[x]:valueCodeableConcept.text</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].text</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.dataAbsentReason</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.interpretation</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.referenceRange</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device</t>
+  </si>
+  <si>
+    <t>va-pre-condition-device</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.id</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.modifierExtension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.code</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.value[x]:valueCodeableConcept.id</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.value[x]:valueCodeableConcept.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.value[x]:valueCodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFVitalsQualifyingDevice</t>
+  </si>
+  <si>
+    <t>1803: terminologyMaps using VF_VitalsQualifyingDevice on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.value[x]:valueCodeableConcept.text</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.dataAbsentReason</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.interpretation</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.referenceRange</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size</t>
+  </si>
+  <si>
+    <t>va-cuff-size</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.id</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.modifierExtension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.code</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept.id</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFVitalsCuffSize</t>
+  </si>
+  <si>
+    <t>1805: terminologyMaps using VF_VitalsCuffSize on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept.text</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.dataAbsentReason</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.interpretation</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.referenceRange</t>
   </si>
 </sst>
 </file>
@@ -2615,7 +2751,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR102"/>
+  <dimension ref="A1:AR139"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="91.8671875" customWidth="true" bestFit="true"/>
@@ -2643,7 +2779,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.83984375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="51.3125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -2653,7 +2789,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="144.703125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="148.453125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="98.75" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
@@ -13846,16 +13982,14 @@
         <v>84</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>692</v>
+      </c>
+      <c r="AC89" s="2"/>
       <c r="AD89" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>84</v>
+        <v>143</v>
       </c>
       <c r="AF89" t="s" s="2">
         <v>687</v>
@@ -13870,10 +14004,10 @@
         <v>84</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>84</v>
@@ -13885,10 +14019,10 @@
         <v>84</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>84</v>
@@ -13899,10 +14033,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14023,10 +14157,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14149,10 +14283,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14277,10 +14411,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14306,16 +14440,16 @@
         <v>171</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>84</v>
@@ -14364,7 +14498,7 @@
         <v>84</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>94</v>
@@ -14388,7 +14522,7 @@
         <v>84</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>378</v>
@@ -14405,10 +14539,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14434,13 +14568,13 @@
         <v>459</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="O94" t="s" s="2">
         <v>463</v>
@@ -14480,17 +14614,19 @@
         <v>84</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="AC94" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD94" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>143</v>
+        <v>84</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14499,7 +14635,7 @@
         <v>94</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>106</v>
@@ -14514,7 +14650,7 @@
         <v>84</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>468</v>
@@ -14531,14 +14667,12 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>705</v>
-      </c>
-      <c r="C95" t="s" s="2">
         <v>712</v>
       </c>
+      <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
         <v>84</v>
       </c>
@@ -14556,22 +14690,22 @@
         <v>84</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K95" t="s" s="2">
         <v>171</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>463</v>
+        <v>557</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>84</v>
@@ -14599,10 +14733,10 @@
         <v>214</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>464</v>
+        <v>558</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>465</v>
+        <v>559</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>84</v>
@@ -14620,7 +14754,7 @@
         <v>84</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14629,13 +14763,13 @@
         <v>94</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>84</v>
+        <v>717</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>84</v>
@@ -14644,38 +14778,38 @@
         <v>84</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>710</v>
+        <v>84</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>468</v>
+        <v>137</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>469</v>
+        <v>562</v>
       </c>
       <c r="AQ95" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR95" t="s" s="2">
-        <v>470</v>
+        <v>84</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>84</v>
+        <v>564</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>84</v>
@@ -14687,16 +14821,20 @@
         <v>84</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>153</v>
+        <v>565</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
+        <v>566</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>568</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>84</v>
       </c>
@@ -14720,13 +14858,13 @@
         <v>84</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>84</v>
+        <v>214</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>84</v>
+        <v>569</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>84</v>
+        <v>570</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>84</v>
@@ -14744,19 +14882,19 @@
         <v>84</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>155</v>
+        <v>718</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>84</v>
@@ -14768,31 +14906,31 @@
         <v>84</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>84</v>
+        <v>571</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>84</v>
+        <v>572</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>157</v>
+        <v>573</v>
       </c>
       <c r="AQ96" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR96" t="s" s="2">
-        <v>84</v>
+        <v>574</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>180</v>
+        <v>84</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -14811,18 +14949,20 @@
         <v>84</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>139</v>
+        <v>85</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>198</v>
+        <v>720</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>199</v>
+        <v>721</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O97" s="2"/>
+        <v>625</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>626</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>84</v>
       </c>
@@ -14858,19 +14998,19 @@
         <v>84</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>142</v>
+        <v>84</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>160</v>
+        <v>84</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>143</v>
+        <v>84</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>161</v>
+        <v>719</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>
@@ -14882,7 +15022,7 @@
         <v>84</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>84</v>
@@ -14897,10 +15037,10 @@
         <v>84</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>84</v>
+        <v>628</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>157</v>
+        <v>629</v>
       </c>
       <c r="AQ97" t="s" s="2">
         <v>84</v>
@@ -14911,12 +15051,14 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>717</v>
+        <v>722</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="C98" s="2"/>
+        <v>687</v>
+      </c>
+      <c r="C98" t="s" s="2">
+        <v>723</v>
+      </c>
       <c r="D98" t="s" s="2">
         <v>84</v>
       </c>
@@ -14925,7 +15067,7 @@
         <v>82</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>95</v>
@@ -14937,19 +15079,19 @@
         <v>95</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>302</v>
+        <v>622</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>303</v>
+        <v>688</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>304</v>
+        <v>689</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>305</v>
+        <v>690</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>306</v>
+        <v>691</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>84</v>
@@ -14974,11 +15116,13 @@
         <v>84</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="Y98" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z98" t="s" s="2">
-        <v>719</v>
+        <v>84</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>84</v>
@@ -14996,7 +15140,7 @@
         <v>84</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>307</v>
+        <v>687</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>82</v>
@@ -15008,10 +15152,10 @@
         <v>84</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>106</v>
+        <v>693</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>720</v>
+        <v>84</v>
       </c>
       <c r="AL98" t="s" s="2">
         <v>84</v>
@@ -15023,10 +15167,10 @@
         <v>84</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>308</v>
+        <v>695</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>309</v>
+        <v>696</v>
       </c>
       <c r="AQ98" t="s" s="2">
         <v>84</v>
@@ -15037,10 +15181,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>722</v>
+        <v>697</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15060,23 +15204,19 @@
         <v>84</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K99" t="s" s="2">
         <v>196</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>361</v>
+        <v>153</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>364</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="N99" s="2"/>
+      <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>84</v>
       </c>
@@ -15124,7 +15264,7 @@
         <v>84</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>365</v>
+        <v>155</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -15136,7 +15276,7 @@
         <v>84</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>84</v>
@@ -15151,10 +15291,10 @@
         <v>84</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>366</v>
+        <v>84</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>367</v>
+        <v>157</v>
       </c>
       <c r="AQ99" t="s" s="2">
         <v>84</v>
@@ -15165,24 +15305,24 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>723</v>
+        <v>698</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I100" t="s" s="2">
         <v>84</v>
@@ -15191,20 +15331,18 @@
         <v>84</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>724</v>
+        <v>198</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>725</v>
+        <v>199</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>726</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>557</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>84</v>
       </c>
@@ -15228,13 +15366,13 @@
         <v>84</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>558</v>
+        <v>84</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>559</v>
+        <v>84</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>84</v>
@@ -15252,22 +15390,22 @@
         <v>84</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>723</v>
+        <v>161</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>727</v>
+        <v>84</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>728</v>
+        <v>84</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>84</v>
@@ -15279,10 +15417,10 @@
         <v>84</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>562</v>
+        <v>157</v>
       </c>
       <c r="AQ100" t="s" s="2">
         <v>84</v>
@@ -15293,14 +15431,14 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>729</v>
+        <v>699</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>564</v>
+        <v>633</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -15313,25 +15451,25 @@
         <v>84</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>565</v>
+        <v>634</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>566</v>
+        <v>635</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>567</v>
+        <v>183</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>568</v>
+        <v>184</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>84</v>
@@ -15356,13 +15494,13 @@
         <v>84</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>569</v>
+        <v>84</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>570</v>
+        <v>84</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>84</v>
@@ -15380,7 +15518,7 @@
         <v>84</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>729</v>
+        <v>636</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15392,7 +15530,7 @@
         <v>84</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>84</v>
@@ -15404,27 +15542,27 @@
         <v>84</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>571</v>
+        <v>84</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>572</v>
+        <v>84</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>573</v>
+        <v>137</v>
       </c>
       <c r="AQ101" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>574</v>
+        <v>84</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>730</v>
+        <v>700</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15432,34 +15570,34 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>731</v>
+        <v>701</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>732</v>
+        <v>702</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>625</v>
+        <v>703</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>626</v>
+        <v>704</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>84</v>
@@ -15484,13 +15622,13 @@
         <v>84</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>84</v>
+        <v>214</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>84</v>
+        <v>374</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>84</v>
+        <v>375</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>84</v>
@@ -15508,13 +15646,13 @@
         <v>84</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>730</v>
+        <v>700</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>84</v>
@@ -15532,23 +15670,4727 @@
         <v>84</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>84</v>
+        <v>705</v>
       </c>
       <c r="AO102" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AP102" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AQ102" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AR102" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="103" hidden="true">
+      <c r="A103" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="O103" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="P103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AC103" s="2"/>
+      <c r="AD103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="AO103" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AP103" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AQ103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR103" t="s" s="2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="104" hidden="true">
+      <c r="A104" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="C104" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="D104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="O104" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="P104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="AO104" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AP104" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AQ104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR104" t="s" s="2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="105" hidden="true">
+      <c r="A105" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="N105" s="2"/>
+      <c r="O105" s="2"/>
+      <c r="P105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP105" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR105" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="106" hidden="true">
+      <c r="A106" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O106" s="2"/>
+      <c r="P106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP106" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR106" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="107" hidden="true">
+      <c r="A107" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="P107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Y107" s="2"/>
+      <c r="Z107" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO107" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AP107" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AQ107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR107" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="108" hidden="true">
+      <c r="A108" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E108" s="2"/>
+      <c r="F108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="O108" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="P108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q108" s="2"/>
+      <c r="R108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO108" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AP108" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AQ108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR108" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="109" hidden="true">
+      <c r="A109" t="s" s="2">
+        <v>741</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E109" s="2"/>
+      <c r="F109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G109" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="P109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q109" s="2"/>
+      <c r="R109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF109" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO109" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AP109" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AQ109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR109" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="110" hidden="true">
+      <c r="A110" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="E110" s="2"/>
+      <c r="F110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="O110" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="P110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q110" s="2"/>
+      <c r="R110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF110" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="AG110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN110" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AO110" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AP110" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AQ110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR110" t="s" s="2">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="111" hidden="true">
+      <c r="A111" t="s" s="2">
+        <v>743</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="C111" s="2"/>
+      <c r="D111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E111" s="2"/>
+      <c r="F111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="P111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q111" s="2"/>
+      <c r="R111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF111" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="AG111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO111" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="AP102" t="s" s="2">
+      <c r="AP111" t="s" s="2">
         <v>629</v>
       </c>
-      <c r="AQ102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR102" t="s" s="2">
+      <c r="AQ111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR111" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="112" hidden="true">
+      <c r="A112" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="C112" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="D112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E112" s="2"/>
+      <c r="F112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="O112" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="P112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q112" s="2"/>
+      <c r="R112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO112" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="AP112" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="AQ112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR112" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="113" hidden="true">
+      <c r="A113" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="C113" s="2"/>
+      <c r="D113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E113" s="2"/>
+      <c r="F113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="N113" s="2"/>
+      <c r="O113" s="2"/>
+      <c r="P113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q113" s="2"/>
+      <c r="R113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP113" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR113" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="114" hidden="true">
+      <c r="A114" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="E114" s="2"/>
+      <c r="F114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O114" s="2"/>
+      <c r="P114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q114" s="2"/>
+      <c r="R114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP114" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR114" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="115" hidden="true">
+      <c r="A115" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="C115" s="2"/>
+      <c r="D115" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="E115" s="2"/>
+      <c r="F115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O115" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="P115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q115" s="2"/>
+      <c r="R115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP115" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AQ115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR115" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="116" hidden="true">
+      <c r="A116" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="C116" s="2"/>
+      <c r="D116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E116" s="2"/>
+      <c r="F116" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G116" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="O116" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="P116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q116" s="2"/>
+      <c r="R116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="Z116" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN116" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="AO116" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AP116" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AQ116" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AR116" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="117" hidden="true">
+      <c r="A117" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E117" s="2"/>
+      <c r="F117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="P117" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q117" s="2"/>
+      <c r="R117" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S117" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AC117" s="2"/>
+      <c r="AD117" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL117" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM117" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN117" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="AO117" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AP117" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AQ117" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR117" t="s" s="2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="118" hidden="true">
+      <c r="A118" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="C118" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="D118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E118" s="2"/>
+      <c r="F118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G118" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H118" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J118" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K118" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="O118" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="P118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q118" s="2"/>
+      <c r="R118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X118" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="Z118" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF118" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="AG118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI118" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="AJ118" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN118" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="AO118" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AP118" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AQ118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR118" t="s" s="2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="119" hidden="true">
+      <c r="A119" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="C119" s="2"/>
+      <c r="D119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E119" s="2"/>
+      <c r="F119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G119" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K119" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M119" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="N119" s="2"/>
+      <c r="O119" s="2"/>
+      <c r="P119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q119" s="2"/>
+      <c r="R119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF119" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP119" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ119" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR119" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="120" hidden="true">
+      <c r="A120" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="C120" s="2"/>
+      <c r="D120" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="E120" s="2"/>
+      <c r="F120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L120" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O120" s="2"/>
+      <c r="P120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q120" s="2"/>
+      <c r="R120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AF120" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ120" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP120" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR120" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="121" hidden="true">
+      <c r="A121" t="s" s="2">
+        <v>754</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="C121" s="2"/>
+      <c r="D121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E121" s="2"/>
+      <c r="F121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H121" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J121" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K121" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L121" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="O121" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="P121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q121" s="2"/>
+      <c r="R121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X121" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Y121" s="2"/>
+      <c r="Z121" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF121" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AG121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ121" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK121" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="AL121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO121" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AP121" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AQ121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR121" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="122" hidden="true">
+      <c r="A122" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="C122" s="2"/>
+      <c r="D122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E122" s="2"/>
+      <c r="F122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G122" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J122" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K122" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L122" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M122" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="N122" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="O122" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="P122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q122" s="2"/>
+      <c r="R122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF122" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AG122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ122" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO122" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AP122" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AQ122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR122" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="123" hidden="true">
+      <c r="A123" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="C123" s="2"/>
+      <c r="D123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E123" s="2"/>
+      <c r="F123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G123" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H123" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K123" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="O123" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="P123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q123" s="2"/>
+      <c r="R123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X123" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="Z123" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AA123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF123" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="AG123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH123" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI123" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="AJ123" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO123" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AP123" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AQ123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR123" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="124" hidden="true">
+      <c r="A124" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="C124" s="2"/>
+      <c r="D124" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="E124" s="2"/>
+      <c r="F124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K124" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L124" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="M124" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="O124" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="P124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q124" s="2"/>
+      <c r="R124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X124" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="Z124" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF124" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="AG124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ124" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN124" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AO124" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AP124" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AQ124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR124" t="s" s="2">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="125" hidden="true">
+      <c r="A125" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="C125" s="2"/>
+      <c r="D125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E125" s="2"/>
+      <c r="F125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K125" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L125" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="M125" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="O125" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="P125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q125" s="2"/>
+      <c r="R125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF125" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="AG125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ125" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO125" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="AP125" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="AQ125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR125" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="126" hidden="true">
+      <c r="A126" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="C126" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="D126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E126" s="2"/>
+      <c r="F126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G126" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H126" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J126" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K126" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="L126" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="M126" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="O126" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="P126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q126" s="2"/>
+      <c r="R126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF126" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="AG126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ126" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="AK126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO126" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="AP126" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="AQ126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR126" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="127" hidden="true">
+      <c r="A127" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="C127" s="2"/>
+      <c r="D127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E127" s="2"/>
+      <c r="F127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G127" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K127" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L127" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="N127" s="2"/>
+      <c r="O127" s="2"/>
+      <c r="P127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q127" s="2"/>
+      <c r="R127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF127" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AG127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH127" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP127" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR127" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="128" hidden="true">
+      <c r="A128" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="C128" s="2"/>
+      <c r="D128" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="E128" s="2"/>
+      <c r="F128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K128" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L128" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="M128" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N128" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O128" s="2"/>
+      <c r="P128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q128" s="2"/>
+      <c r="R128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF128" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ128" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP128" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR128" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="129" hidden="true">
+      <c r="A129" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="C129" s="2"/>
+      <c r="D129" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="E129" s="2"/>
+      <c r="F129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I129" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="J129" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K129" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L129" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="M129" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O129" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="P129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q129" s="2"/>
+      <c r="R129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF129" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AG129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ129" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP129" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AQ129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR129" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="130" hidden="true">
+      <c r="A130" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="C130" s="2"/>
+      <c r="D130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E130" s="2"/>
+      <c r="F130" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G130" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H130" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J130" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K130" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L130" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="M130" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="N130" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="O130" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="P130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q130" s="2"/>
+      <c r="R130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X130" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y130" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="Z130" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AA130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF130" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="AG130" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AH130" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ130" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM130" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN130" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="AO130" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AP130" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AQ130" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AR130" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="131" hidden="true">
+      <c r="A131" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="C131" s="2"/>
+      <c r="D131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E131" s="2"/>
+      <c r="F131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G131" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H131" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J131" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K131" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="L131" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="O131" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="P131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q131" s="2"/>
+      <c r="R131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X131" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="Z131" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AA131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AC131" s="2"/>
+      <c r="AD131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AF131" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="AG131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH131" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI131" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="AJ131" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN131" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="AO131" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AP131" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AQ131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR131" t="s" s="2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="132" hidden="true">
+      <c r="A132" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="C132" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="D132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E132" s="2"/>
+      <c r="F132" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G132" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H132" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J132" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K132" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L132" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="M132" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="O132" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="P132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q132" s="2"/>
+      <c r="R132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X132" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y132" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="Z132" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AA132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF132" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="AG132" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH132" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI132" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="AJ132" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN132" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="AO132" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AP132" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AQ132" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR132" t="s" s="2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="133" hidden="true">
+      <c r="A133" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="C133" s="2"/>
+      <c r="D133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E133" s="2"/>
+      <c r="F133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G133" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K133" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L133" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M133" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="N133" s="2"/>
+      <c r="O133" s="2"/>
+      <c r="P133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q133" s="2"/>
+      <c r="R133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF133" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AG133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH133" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP133" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ133" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR133" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="134" hidden="true">
+      <c r="A134" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="C134" s="2"/>
+      <c r="D134" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="E134" s="2"/>
+      <c r="F134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K134" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L134" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="M134" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N134" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O134" s="2"/>
+      <c r="P134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q134" s="2"/>
+      <c r="R134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB134" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AD134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE134" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AF134" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ134" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP134" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ134" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR134" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="135" hidden="true">
+      <c r="A135" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="C135" s="2"/>
+      <c r="D135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E135" s="2"/>
+      <c r="F135" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H135" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J135" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K135" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L135" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M135" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="N135" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="O135" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="P135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q135" s="2"/>
+      <c r="R135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X135" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Y135" s="2"/>
+      <c r="Z135" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="AA135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF135" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AG135" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ135" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK135" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="AL135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO135" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AP135" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AQ135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR135" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="136" hidden="true">
+      <c r="A136" t="s" s="2">
+        <v>774</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="C136" s="2"/>
+      <c r="D136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E136" s="2"/>
+      <c r="F136" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G136" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J136" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K136" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L136" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M136" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="N136" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="O136" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="P136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q136" s="2"/>
+      <c r="R136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF136" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AG136" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH136" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ136" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO136" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AP136" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AQ136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR136" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="137" hidden="true">
+      <c r="A137" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="C137" s="2"/>
+      <c r="D137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E137" s="2"/>
+      <c r="F137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G137" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H137" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K137" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L137" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="M137" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="N137" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="O137" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="P137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q137" s="2"/>
+      <c r="R137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X137" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y137" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="Z137" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AA137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF137" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="AG137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH137" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI137" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="AJ137" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO137" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AP137" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AQ137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR137" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="138" hidden="true">
+      <c r="A138" t="s" s="2">
+        <v>776</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="C138" s="2"/>
+      <c r="D138" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="E138" s="2"/>
+      <c r="F138" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G138" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K138" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L138" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="M138" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="N138" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="O138" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="P138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q138" s="2"/>
+      <c r="R138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X138" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y138" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="Z138" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AA138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF138" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="AG138" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH138" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ138" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN138" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AO138" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AP138" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AQ138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR138" t="s" s="2">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="139" hidden="true">
+      <c r="A139" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="C139" s="2"/>
+      <c r="D139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E139" s="2"/>
+      <c r="F139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K139" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L139" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="M139" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="N139" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="O139" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="P139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q139" s="2"/>
+      <c r="R139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF139" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="AG139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ139" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO139" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="AP139" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="AQ139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR139" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR102">
+  <autoFilter ref="A1:AR139">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15558,7 +20400,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI101">
+  <conditionalFormatting sqref="A2:AI138">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5635" uniqueCount="778">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5635" uniqueCount="785">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -713,10 +713,16 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
+    <t>http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+  </si>
+  <si>
     <t>http://www.acme.com/identifiers/patient</t>
   </si>
   <si>
     <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>660-1: fixed value = http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>
@@ -2287,6 +2293,18 @@
     <t>Observation.component:va-pre-condition.code</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="104158-1"/&gt;
+    &lt;display value="Associated precondition - Reported"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>1802-1: fixed value = http://loinc.org#104158-1 Associated precondition - Reported</t>
+  </si>
+  <si>
     <t>Observation.component:va-pre-condition.value[x]</t>
   </si>
   <si>
@@ -2353,6 +2371,9 @@
     <t>Observation.component:va-pre-condition-device.code</t>
   </si>
   <si>
+    <t>1803-1: fixed value = http://loinc.org#104158-1 Associated precondition - Reported</t>
+  </si>
+  <si>
     <t>Observation.component:va-pre-condition-device.value[x]</t>
   </si>
   <si>
@@ -2402,6 +2423,18 @@
   </si>
   <si>
     <t>Observation.component:va-cuff-size.code</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="8358-4"/&gt;
+    &lt;display value="Blood pressure device cuff size"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>1805-1: fixed value = http://loinc.org#8358-4 Blood pressure device cuff size</t>
   </si>
   <si>
     <t>Observation.component:va-cuff-size.value[x]</t>
@@ -5336,7 +5369,7 @@
         <v>94</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>84</v>
@@ -5367,10 +5400,10 @@
         <v>84</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>84</v>
+        <v>224</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="U21" t="s" s="2">
         <v>84</v>
@@ -5406,7 +5439,7 @@
         <v>84</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -5421,7 +5454,7 @@
         <v>106</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>84</v>
+        <v>227</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>84</v>
@@ -5433,10 +5466,10 @@
         <v>84</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AQ21" t="s" s="2">
         <v>84</v>
@@ -5447,10 +5480,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5476,13 +5509,13 @@
         <v>196</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -5496,7 +5529,7 @@
         <v>84</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="U22" t="s" s="2">
         <v>84</v>
@@ -5532,7 +5565,7 @@
         <v>84</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
@@ -5547,7 +5580,7 @@
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>84</v>
@@ -5559,10 +5592,10 @@
         <v>84</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AQ22" t="s" s="2">
         <v>84</v>
@@ -5573,10 +5606,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5599,13 +5632,13 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -5656,7 +5689,7 @@
         <v>84</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -5683,10 +5716,10 @@
         <v>84</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AQ23" t="s" s="2">
         <v>84</v>
@@ -5697,10 +5730,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5723,16 +5756,16 @@
         <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5782,7 +5815,7 @@
         <v>84</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -5809,10 +5842,10 @@
         <v>84</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AQ24" t="s" s="2">
         <v>84</v>
@@ -5823,14 +5856,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5849,17 +5882,17 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>84</v>
@@ -5908,7 +5941,7 @@
         <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -5929,16 +5962,16 @@
         <v>84</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AQ25" t="s" s="2">
         <v>84</v>
@@ -5949,14 +5982,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5975,16 +6008,16 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -6034,7 +6067,7 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -6055,16 +6088,16 @@
         <v>84</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>84</v>
@@ -6075,10 +6108,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -6104,16 +6137,16 @@
         <v>114</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>84</v>
@@ -6142,7 +6175,7 @@
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>84</v>
@@ -6160,7 +6193,7 @@
         <v>84</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>94</v>
@@ -6175,25 +6208,25 @@
         <v>106</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AR27" t="s" s="2">
         <v>84</v>
@@ -6201,10 +6234,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6230,16 +6263,16 @@
         <v>171</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -6249,7 +6282,7 @@
         <v>84</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>84</v>
@@ -6267,16 +6300,16 @@
         <v>118</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AC28" s="2"/>
       <c r="AD28" t="s" s="2">
@@ -6286,7 +6319,7 @@
         <v>143</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -6301,7 +6334,7 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>84</v>
@@ -6316,10 +6349,10 @@
         <v>84</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>84</v>
@@ -6327,13 +6360,13 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>84</v>
@@ -6358,16 +6391,16 @@
         <v>171</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -6395,10 +6428,10 @@
         <v>118</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>84</v>
@@ -6416,7 +6449,7 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -6446,10 +6479,10 @@
         <v>84</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AR29" t="s" s="2">
         <v>84</v>
@@ -6457,10 +6490,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6581,10 +6614,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6707,10 +6740,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6733,19 +6766,19 @@
         <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -6794,7 +6827,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6821,10 +6854,10 @@
         <v>84</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>84</v>
@@ -6835,10 +6868,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6959,10 +6992,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -7085,10 +7118,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -7114,23 +7147,23 @@
         <v>108</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>84</v>
@@ -7172,7 +7205,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -7199,10 +7232,10 @@
         <v>84</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
@@ -7213,10 +7246,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7242,13 +7275,13 @@
         <v>196</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -7298,7 +7331,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -7325,10 +7358,10 @@
         <v>84</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
@@ -7339,10 +7372,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7368,21 +7401,21 @@
         <v>114</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>84</v>
@@ -7424,7 +7457,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -7451,10 +7484,10 @@
         <v>84</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
@@ -7465,10 +7498,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7494,14 +7527,14 @@
         <v>196</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
@@ -7550,7 +7583,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7577,10 +7610,10 @@
         <v>84</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
@@ -7591,10 +7624,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7617,19 +7650,19 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -7678,7 +7711,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7705,10 +7738,10 @@
         <v>84</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -7719,10 +7752,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7748,16 +7781,16 @@
         <v>196</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7806,7 +7839,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7833,10 +7866,10 @@
         <v>84</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
@@ -7847,14 +7880,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7876,16 +7909,16 @@
         <v>171</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7913,10 +7946,10 @@
         <v>214</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>84</v>
@@ -7934,7 +7967,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>94</v>
@@ -7955,30 +7988,30 @@
         <v>84</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -8099,10 +8132,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8225,10 +8258,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8251,19 +8284,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -8292,7 +8325,7 @@
       </c>
       <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>84</v>
@@ -8310,7 +8343,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -8325,10 +8358,10 @@
         <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>84</v>
@@ -8337,10 +8370,10 @@
         <v>84</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -8351,10 +8384,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8380,16 +8413,16 @@
         <v>196</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -8438,7 +8471,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8465,10 +8498,10 @@
         <v>84</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -8479,10 +8512,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8505,19 +8538,19 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -8566,7 +8599,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8581,25 +8614,25 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>84</v>
@@ -8607,10 +8640,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8633,16 +8666,16 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8692,7 +8725,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8719,13 +8752,13 @@
         <v>84</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>84</v>
@@ -8733,14 +8766,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -8759,19 +8792,19 @@
         <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
@@ -8820,7 +8853,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8841,19 +8874,19 @@
         <v>84</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>84</v>
@@ -8861,14 +8894,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -8887,19 +8920,19 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
@@ -8936,7 +8969,7 @@
         <v>84</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AC49" s="2"/>
       <c r="AD49" t="s" s="2">
@@ -8946,7 +8979,7 @@
         <v>143</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8955,10 +8988,10 @@
         <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>84</v>
@@ -8967,19 +9000,19 @@
         <v>84</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>84</v>
@@ -8987,16 +9020,16 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -9015,19 +9048,19 @@
         <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -9076,7 +9109,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -9085,31 +9118,31 @@
         <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>84</v>
@@ -9117,10 +9150,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9143,16 +9176,16 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -9202,7 +9235,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -9217,10 +9250,10 @@
         <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>84</v>
@@ -9229,13 +9262,13 @@
         <v>84</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>84</v>
@@ -9243,10 +9276,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9269,17 +9302,17 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -9328,7 +9361,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9343,25 +9376,25 @@
         <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>84</v>
@@ -9369,10 +9402,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9395,19 +9428,19 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>84</v>
@@ -9435,16 +9468,16 @@
         <v>214</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AC53" s="2"/>
       <c r="AD53" t="s" s="2">
@@ -9454,7 +9487,7 @@
         <v>143</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -9463,7 +9496,7 @@
         <v>94</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>106</v>
@@ -9478,30 +9511,30 @@
         <v>84</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR53" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>84</v>
@@ -9523,19 +9556,19 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>84</v>
@@ -9563,10 +9596,10 @@
         <v>214</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>84</v>
@@ -9584,7 +9617,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9593,7 +9626,7 @@
         <v>94</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>106</v>
@@ -9608,27 +9641,27 @@
         <v>84</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR54" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9749,10 +9782,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9875,10 +9908,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9901,19 +9934,19 @@
         <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>84</v>
@@ -9962,7 +9995,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9977,10 +10010,10 @@
         <v>106</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>84</v>
@@ -9989,10 +10022,10 @@
         <v>84</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -10003,10 +10036,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10032,20 +10065,20 @@
         <v>114</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q58" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="R58" t="s" s="2">
         <v>84</v>
@@ -10069,10 +10102,10 @@
         <v>174</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
@@ -10090,7 +10123,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -10117,10 +10150,10 @@
         <v>84</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -10131,10 +10164,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10160,14 +10193,14 @@
         <v>196</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -10216,7 +10249,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10243,10 +10276,10 @@
         <v>84</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -10257,10 +10290,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10286,14 +10319,14 @@
         <v>108</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -10342,7 +10375,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10351,7 +10384,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -10369,10 +10402,10 @@
         <v>84</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -10383,10 +10416,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10412,16 +10445,16 @@
         <v>114</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
@@ -10470,7 +10503,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -10485,10 +10518,10 @@
         <v>106</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>84</v>
@@ -10497,10 +10530,10 @@
         <v>84</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -10511,10 +10544,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10540,10 +10573,10 @@
         <v>196</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10635,10 +10668,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10757,13 +10790,13 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>84</v>
@@ -10785,16 +10818,16 @@
         <v>84</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10885,10 +10918,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -11009,10 +11042,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11133,10 +11166,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11176,7 +11209,7 @@
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="S67" t="s" s="2">
         <v>84</v>
@@ -11259,10 +11292,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11285,7 +11318,7 @@
         <v>84</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="L68" t="s" s="2">
         <v>172</v>
@@ -11303,7 +11336,7 @@
         <v>84</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>84</v>
@@ -11383,10 +11416,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11412,10 +11445,10 @@
         <v>196</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -11466,7 +11499,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11507,10 +11540,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11536,16 +11569,16 @@
         <v>171</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>84</v>
@@ -11573,10 +11606,10 @@
         <v>214</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>84</v>
@@ -11594,7 +11627,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11603,13 +11636,13 @@
         <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>84</v>
@@ -11624,7 +11657,7 @@
         <v>137</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
@@ -11635,14 +11668,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -11664,16 +11697,16 @@
         <v>171</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
@@ -11701,10 +11734,10 @@
         <v>214</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>84</v>
@@ -11722,7 +11755,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11746,27 +11779,27 @@
         <v>84</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11789,19 +11822,19 @@
         <v>84</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>84</v>
@@ -11850,7 +11883,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11877,10 +11910,10 @@
         <v>84</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>
@@ -11891,10 +11924,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11920,13 +11953,13 @@
         <v>171</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11952,13 +11985,13 @@
         <v>84</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>84</v>
@@ -11976,7 +12009,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -12000,27 +12033,27 @@
         <v>84</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12046,16 +12079,16 @@
         <v>171</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>84</v>
@@ -12084,7 +12117,7 @@
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>84</v>
@@ -12102,7 +12135,7 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -12117,7 +12150,7 @@
         <v>106</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>84</v>
@@ -12129,10 +12162,10 @@
         <v>84</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AQ74" t="s" s="2">
         <v>84</v>
@@ -12143,10 +12176,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12169,16 +12202,16 @@
         <v>84</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12228,7 +12261,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12252,27 +12285,27 @@
         <v>84</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR75" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12295,16 +12328,16 @@
         <v>84</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -12354,7 +12387,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12378,27 +12411,27 @@
         <v>84</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR76" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12421,19 +12454,19 @@
         <v>84</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>84</v>
@@ -12482,7 +12515,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12494,7 +12527,7 @@
         <v>84</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>84</v>
@@ -12509,10 +12542,10 @@
         <v>84</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>84</v>
@@ -12523,10 +12556,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12647,10 +12680,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12773,14 +12806,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -12802,10 +12835,10 @@
         <v>139</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>183</v>
@@ -12860,7 +12893,7 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -12901,10 +12934,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12927,13 +12960,13 @@
         <v>84</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -12984,7 +13017,7 @@
         <v>84</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -12993,7 +13026,7 @@
         <v>94</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>106</v>
@@ -13011,10 +13044,10 @@
         <v>84</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AQ81" t="s" s="2">
         <v>84</v>
@@ -13025,10 +13058,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13051,13 +13084,13 @@
         <v>84</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -13108,7 +13141,7 @@
         <v>84</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -13117,7 +13150,7 @@
         <v>94</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>106</v>
@@ -13135,10 +13168,10 @@
         <v>84</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>84</v>
@@ -13149,10 +13182,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13178,16 +13211,16 @@
         <v>171</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>84</v>
@@ -13215,10 +13248,10 @@
         <v>118</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>84</v>
@@ -13236,7 +13269,7 @@
         <v>84</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13260,13 +13293,13 @@
         <v>84</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AQ83" t="s" s="2">
         <v>84</v>
@@ -13277,10 +13310,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13306,16 +13339,16 @@
         <v>171</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>84</v>
@@ -13340,13 +13373,13 @@
         <v>84</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>84</v>
@@ -13364,7 +13397,7 @@
         <v>84</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13388,13 +13421,13 @@
         <v>84</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AQ84" t="s" s="2">
         <v>84</v>
@@ -13405,10 +13438,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13431,17 +13464,17 @@
         <v>84</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>84</v>
@@ -13490,7 +13523,7 @@
         <v>84</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -13520,7 +13553,7 @@
         <v>84</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="AQ85" t="s" s="2">
         <v>84</v>
@@ -13531,10 +13564,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13560,10 +13593,10 @@
         <v>196</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -13614,7 +13647,7 @@
         <v>84</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
@@ -13641,10 +13674,10 @@
         <v>84</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>84</v>
@@ -13655,10 +13688,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13681,16 +13714,16 @@
         <v>95</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -13740,7 +13773,7 @@
         <v>84</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13767,10 +13800,10 @@
         <v>84</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>84</v>
@@ -13781,10 +13814,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13807,16 +13840,16 @@
         <v>95</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -13866,7 +13899,7 @@
         <v>84</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13893,10 +13926,10 @@
         <v>84</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="AQ88" t="s" s="2">
         <v>84</v>
@@ -13907,10 +13940,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13933,19 +13966,19 @@
         <v>95</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>84</v>
@@ -13982,7 +14015,7 @@
         <v>84</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="AC89" s="2"/>
       <c r="AD89" t="s" s="2">
@@ -13992,7 +14025,7 @@
         <v>143</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -14004,10 +14037,10 @@
         <v>84</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>84</v>
@@ -14019,10 +14052,10 @@
         <v>84</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>84</v>
@@ -14033,10 +14066,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14157,10 +14190,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14283,14 +14316,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -14312,10 +14345,10 @@
         <v>139</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="N92" t="s" s="2">
         <v>183</v>
@@ -14370,7 +14403,7 @@
         <v>84</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14411,10 +14444,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14440,16 +14473,16 @@
         <v>171</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>84</v>
@@ -14477,10 +14510,10 @@
         <v>214</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>84</v>
@@ -14498,7 +14531,7 @@
         <v>84</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>94</v>
@@ -14522,16 +14555,16 @@
         <v>84</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AQ93" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AR93" t="s" s="2">
         <v>84</v>
@@ -14539,10 +14572,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14565,19 +14598,19 @@
         <v>95</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>84</v>
@@ -14605,10 +14638,10 @@
         <v>214</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>84</v>
@@ -14626,7 +14659,7 @@
         <v>84</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14635,7 +14668,7 @@
         <v>94</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>106</v>
@@ -14650,27 +14683,27 @@
         <v>84</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AQ94" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR94" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14696,16 +14729,16 @@
         <v>171</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>84</v>
@@ -14733,10 +14766,10 @@
         <v>214</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>84</v>
@@ -14754,7 +14787,7 @@
         <v>84</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14763,13 +14796,13 @@
         <v>94</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>84</v>
@@ -14784,7 +14817,7 @@
         <v>137</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AQ95" t="s" s="2">
         <v>84</v>
@@ -14795,14 +14828,14 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -14824,16 +14857,16 @@
         <v>171</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>84</v>
@@ -14861,10 +14894,10 @@
         <v>214</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>84</v>
@@ -14882,7 +14915,7 @@
         <v>84</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14906,27 +14939,27 @@
         <v>84</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AQ96" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR96" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14952,16 +14985,16 @@
         <v>85</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>84</v>
@@ -15010,7 +15043,7 @@
         <v>84</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>
@@ -15037,10 +15070,10 @@
         <v>84</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AQ97" t="s" s="2">
         <v>84</v>
@@ -15051,13 +15084,13 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="D98" t="s" s="2">
         <v>84</v>
@@ -15079,19 +15112,19 @@
         <v>95</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>84</v>
@@ -15140,7 +15173,7 @@
         <v>84</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>82</v>
@@ -15152,7 +15185,7 @@
         <v>84</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>84</v>
@@ -15167,10 +15200,10 @@
         <v>84</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="AQ98" t="s" s="2">
         <v>84</v>
@@ -15181,10 +15214,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15305,10 +15338,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15431,14 +15464,14 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -15460,10 +15493,10 @@
         <v>139</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="N101" t="s" s="2">
         <v>183</v>
@@ -15518,7 +15551,7 @@
         <v>84</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15559,10 +15592,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15588,16 +15621,16 @@
         <v>171</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>84</v>
@@ -15607,7 +15640,7 @@
         <v>84</v>
       </c>
       <c r="S102" t="s" s="2">
-        <v>84</v>
+        <v>730</v>
       </c>
       <c r="T102" t="s" s="2">
         <v>84</v>
@@ -15625,10 +15658,10 @@
         <v>214</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>84</v>
@@ -15646,7 +15679,7 @@
         <v>84</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>94</v>
@@ -15661,7 +15694,7 @@
         <v>106</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>84</v>
+        <v>731</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>84</v>
@@ -15670,16 +15703,16 @@
         <v>84</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>84</v>
@@ -15687,10 +15720,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15713,19 +15746,19 @@
         <v>95</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>84</v>
@@ -15753,16 +15786,16 @@
         <v>214</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AC103" s="2"/>
       <c r="AD103" t="s" s="2">
@@ -15772,7 +15805,7 @@
         <v>143</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15781,7 +15814,7 @@
         <v>94</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>106</v>
@@ -15796,30 +15829,30 @@
         <v>84</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AQ103" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR103" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>84</v>
@@ -15844,16 +15877,16 @@
         <v>171</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>84</v>
@@ -15881,10 +15914,10 @@
         <v>214</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>84</v>
@@ -15902,7 +15935,7 @@
         <v>84</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15911,7 +15944,7 @@
         <v>94</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>106</v>
@@ -15926,27 +15959,27 @@
         <v>84</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AQ104" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR104" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -16067,10 +16100,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16193,10 +16226,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16219,19 +16252,19 @@
         <v>95</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>84</v>
@@ -16260,7 +16293,7 @@
       </c>
       <c r="Y107" s="2"/>
       <c r="Z107" t="s" s="2">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>84</v>
@@ -16278,7 +16311,7 @@
         <v>84</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>82</v>
@@ -16293,7 +16326,7 @@
         <v>106</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="AL107" t="s" s="2">
         <v>84</v>
@@ -16305,10 +16338,10 @@
         <v>84</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AQ107" t="s" s="2">
         <v>84</v>
@@ -16319,10 +16352,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16348,16 +16381,16 @@
         <v>196</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>84</v>
@@ -16406,7 +16439,7 @@
         <v>84</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>82</v>
@@ -16433,10 +16466,10 @@
         <v>84</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AQ108" t="s" s="2">
         <v>84</v>
@@ -16447,10 +16480,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16476,16 +16509,16 @@
         <v>171</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>84</v>
@@ -16513,10 +16546,10 @@
         <v>214</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>84</v>
@@ -16534,7 +16567,7 @@
         <v>84</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>82</v>
@@ -16543,7 +16576,7 @@
         <v>94</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>106</v>
@@ -16564,7 +16597,7 @@
         <v>137</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AQ109" t="s" s="2">
         <v>84</v>
@@ -16575,14 +16608,14 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -16604,16 +16637,16 @@
         <v>171</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>84</v>
@@ -16641,10 +16674,10 @@
         <v>214</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>84</v>
@@ -16662,7 +16695,7 @@
         <v>84</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>82</v>
@@ -16686,27 +16719,27 @@
         <v>84</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AQ110" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR110" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16732,16 +16765,16 @@
         <v>85</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>84</v>
@@ -16790,7 +16823,7 @@
         <v>84</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>82</v>
@@ -16817,10 +16850,10 @@
         <v>84</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AP111" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AQ111" t="s" s="2">
         <v>84</v>
@@ -16831,13 +16864,13 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="D112" t="s" s="2">
         <v>84</v>
@@ -16859,19 +16892,19 @@
         <v>95</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>84</v>
@@ -16920,7 +16953,7 @@
         <v>84</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>82</v>
@@ -16932,7 +16965,7 @@
         <v>84</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>84</v>
@@ -16947,10 +16980,10 @@
         <v>84</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="AQ112" t="s" s="2">
         <v>84</v>
@@ -16961,10 +16994,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -17085,10 +17118,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17211,14 +17244,14 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
@@ -17240,10 +17273,10 @@
         <v>139</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="N115" t="s" s="2">
         <v>183</v>
@@ -17298,7 +17331,7 @@
         <v>84</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>82</v>
@@ -17339,10 +17372,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17368,16 +17401,16 @@
         <v>171</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>84</v>
@@ -17387,7 +17420,7 @@
         <v>84</v>
       </c>
       <c r="S116" t="s" s="2">
-        <v>84</v>
+        <v>730</v>
       </c>
       <c r="T116" t="s" s="2">
         <v>84</v>
@@ -17405,10 +17438,10 @@
         <v>214</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>84</v>
@@ -17426,7 +17459,7 @@
         <v>84</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>94</v>
@@ -17441,7 +17474,7 @@
         <v>106</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>84</v>
+        <v>754</v>
       </c>
       <c r="AL116" t="s" s="2">
         <v>84</v>
@@ -17450,16 +17483,16 @@
         <v>84</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AQ116" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AR116" t="s" s="2">
         <v>84</v>
@@ -17467,10 +17500,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17493,19 +17526,19 @@
         <v>95</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>84</v>
@@ -17533,16 +17566,16 @@
         <v>214</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB117" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AC117" s="2"/>
       <c r="AD117" t="s" s="2">
@@ -17552,7 +17585,7 @@
         <v>143</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>82</v>
@@ -17561,7 +17594,7 @@
         <v>94</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="AJ117" t="s" s="2">
         <v>106</v>
@@ -17576,30 +17609,30 @@
         <v>84</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AQ117" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR117" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="D118" t="s" s="2">
         <v>84</v>
@@ -17624,16 +17657,16 @@
         <v>171</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>84</v>
@@ -17661,10 +17694,10 @@
         <v>214</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>84</v>
@@ -17682,7 +17715,7 @@
         <v>84</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>82</v>
@@ -17691,7 +17724,7 @@
         <v>94</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="AJ118" t="s" s="2">
         <v>106</v>
@@ -17706,27 +17739,27 @@
         <v>84</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AP118" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AQ118" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR118" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17847,10 +17880,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17973,10 +18006,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>754</v>
+        <v>759</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17999,19 +18032,19 @@
         <v>95</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>84</v>
@@ -18040,7 +18073,7 @@
       </c>
       <c r="Y121" s="2"/>
       <c r="Z121" t="s" s="2">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>84</v>
@@ -18058,7 +18091,7 @@
         <v>84</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>82</v>
@@ -18073,7 +18106,7 @@
         <v>106</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="AL121" t="s" s="2">
         <v>84</v>
@@ -18085,10 +18118,10 @@
         <v>84</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AP121" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AQ121" t="s" s="2">
         <v>84</v>
@@ -18099,10 +18132,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18128,16 +18161,16 @@
         <v>196</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>84</v>
@@ -18186,7 +18219,7 @@
         <v>84</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>82</v>
@@ -18213,10 +18246,10 @@
         <v>84</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AQ122" t="s" s="2">
         <v>84</v>
@@ -18227,10 +18260,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -18256,16 +18289,16 @@
         <v>171</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>84</v>
@@ -18293,10 +18326,10 @@
         <v>214</v>
       </c>
       <c r="Y123" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="Z123" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>84</v>
@@ -18314,7 +18347,7 @@
         <v>84</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>82</v>
@@ -18323,7 +18356,7 @@
         <v>94</v>
       </c>
       <c r="AI123" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="AJ123" t="s" s="2">
         <v>106</v>
@@ -18344,7 +18377,7 @@
         <v>137</v>
       </c>
       <c r="AP123" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AQ123" t="s" s="2">
         <v>84</v>
@@ -18355,14 +18388,14 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
@@ -18384,16 +18417,16 @@
         <v>171</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>84</v>
@@ -18421,10 +18454,10 @@
         <v>214</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>84</v>
@@ -18442,7 +18475,7 @@
         <v>84</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>82</v>
@@ -18466,27 +18499,27 @@
         <v>84</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AP124" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AQ124" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR124" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>760</v>
+        <v>765</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18512,16 +18545,16 @@
         <v>85</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>84</v>
@@ -18570,7 +18603,7 @@
         <v>84</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>82</v>
@@ -18597,10 +18630,10 @@
         <v>84</v>
       </c>
       <c r="AO125" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AP125" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AQ125" t="s" s="2">
         <v>84</v>
@@ -18611,13 +18644,13 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="D126" t="s" s="2">
         <v>84</v>
@@ -18639,19 +18672,19 @@
         <v>95</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>84</v>
@@ -18700,7 +18733,7 @@
         <v>84</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>82</v>
@@ -18712,7 +18745,7 @@
         <v>84</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="AK126" t="s" s="2">
         <v>84</v>
@@ -18727,10 +18760,10 @@
         <v>84</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="AQ126" t="s" s="2">
         <v>84</v>
@@ -18741,10 +18774,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18865,10 +18898,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18991,14 +19024,14 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
@@ -19020,10 +19053,10 @@
         <v>139</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="N129" t="s" s="2">
         <v>183</v>
@@ -19078,7 +19111,7 @@
         <v>84</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>82</v>
@@ -19119,10 +19152,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -19148,16 +19181,16 @@
         <v>171</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>84</v>
@@ -19167,7 +19200,7 @@
         <v>84</v>
       </c>
       <c r="S130" t="s" s="2">
-        <v>84</v>
+        <v>772</v>
       </c>
       <c r="T130" t="s" s="2">
         <v>84</v>
@@ -19185,10 +19218,10 @@
         <v>214</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>84</v>
@@ -19206,7 +19239,7 @@
         <v>84</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>94</v>
@@ -19221,7 +19254,7 @@
         <v>106</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>84</v>
+        <v>773</v>
       </c>
       <c r="AL130" t="s" s="2">
         <v>84</v>
@@ -19230,16 +19263,16 @@
         <v>84</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="AO130" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AP130" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AQ130" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AR130" t="s" s="2">
         <v>84</v>
@@ -19247,10 +19280,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -19273,19 +19306,19 @@
         <v>95</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>84</v>
@@ -19313,16 +19346,16 @@
         <v>214</v>
       </c>
       <c r="Y131" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="Z131" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB131" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AC131" s="2"/>
       <c r="AD131" t="s" s="2">
@@ -19332,7 +19365,7 @@
         <v>143</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>82</v>
@@ -19341,7 +19374,7 @@
         <v>94</v>
       </c>
       <c r="AI131" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="AJ131" t="s" s="2">
         <v>106</v>
@@ -19356,30 +19389,30 @@
         <v>84</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="AO131" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AP131" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AQ131" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR131" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="D132" t="s" s="2">
         <v>84</v>
@@ -19404,16 +19437,16 @@
         <v>171</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>84</v>
@@ -19441,10 +19474,10 @@
         <v>214</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>84</v>
@@ -19462,7 +19495,7 @@
         <v>84</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>82</v>
@@ -19471,7 +19504,7 @@
         <v>94</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="AJ132" t="s" s="2">
         <v>106</v>
@@ -19486,27 +19519,27 @@
         <v>84</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="AO132" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AP132" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AQ132" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR132" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -19627,10 +19660,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -19753,10 +19786,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -19779,19 +19812,19 @@
         <v>95</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>84</v>
@@ -19820,7 +19853,7 @@
       </c>
       <c r="Y135" s="2"/>
       <c r="Z135" t="s" s="2">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>84</v>
@@ -19838,7 +19871,7 @@
         <v>84</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>82</v>
@@ -19853,7 +19886,7 @@
         <v>106</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="AL135" t="s" s="2">
         <v>84</v>
@@ -19865,10 +19898,10 @@
         <v>84</v>
       </c>
       <c r="AO135" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AP135" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AQ135" t="s" s="2">
         <v>84</v>
@@ -19879,10 +19912,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19908,16 +19941,16 @@
         <v>196</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>84</v>
@@ -19966,7 +19999,7 @@
         <v>84</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>82</v>
@@ -19993,10 +20026,10 @@
         <v>84</v>
       </c>
       <c r="AO136" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AP136" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AQ136" t="s" s="2">
         <v>84</v>
@@ -20007,10 +20040,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -20036,16 +20069,16 @@
         <v>171</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>84</v>
@@ -20073,10 +20106,10 @@
         <v>214</v>
       </c>
       <c r="Y137" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="Z137" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>84</v>
@@ -20094,7 +20127,7 @@
         <v>84</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>82</v>
@@ -20103,7 +20136,7 @@
         <v>94</v>
       </c>
       <c r="AI137" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="AJ137" t="s" s="2">
         <v>106</v>
@@ -20124,7 +20157,7 @@
         <v>137</v>
       </c>
       <c r="AP137" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AQ137" t="s" s="2">
         <v>84</v>
@@ -20135,14 +20168,14 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
@@ -20164,16 +20197,16 @@
         <v>171</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>84</v>
@@ -20201,10 +20234,10 @@
         <v>214</v>
       </c>
       <c r="Y138" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="Z138" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AA138" t="s" s="2">
         <v>84</v>
@@ -20222,7 +20255,7 @@
         <v>84</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>82</v>
@@ -20246,27 +20279,27 @@
         <v>84</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AO138" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AP138" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AQ138" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR138" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -20292,16 +20325,16 @@
         <v>85</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>84</v>
@@ -20350,7 +20383,7 @@
         <v>84</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>82</v>
@@ -20377,10 +20410,10 @@
         <v>84</v>
       </c>
       <c r="AO139" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AP139" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AQ139" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
